--- a/backend/data/enterprise.xlsx
+++ b/backend/data/enterprise.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\HL\HLViewer\backend\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\v.vereshchak\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF00187E-D5E7-43C1-954A-1F6B5DF93C71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A210E12A-FE53-45DD-A010-CB742886B3CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3558,6 +3558,15 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -3565,15 +3574,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3909,11 +3909,11 @@
     </row>
     <row r="3" spans="1:12" s="1" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
+      <c r="A4" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
       <c r="D4" s="3" t="s">
         <v>2</v>
       </c>
@@ -3938,16 +3938,16 @@
       <c r="K4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="L4" s="11" t="s">
+      <c r="L4" s="6" t="s">
         <v>1130</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
       <c r="D5" s="4" t="s">
         <v>10</v>
       </c>
@@ -3977,11 +3977,11 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
       <c r="D6" s="4" t="s">
         <v>18</v>
       </c>
@@ -4011,11 +4011,11 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
       <c r="D7" s="4" t="s">
         <v>24</v>
       </c>
@@ -4045,11 +4045,11 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
       <c r="D8" s="4" t="s">
         <v>28</v>
       </c>
@@ -4079,11 +4079,11 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
       <c r="D9" s="4" t="s">
         <v>33</v>
       </c>
@@ -4113,11 +4113,11 @@
       </c>
     </row>
     <row r="10" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
       <c r="D10" s="4" t="s">
         <v>38</v>
       </c>
@@ -4147,11 +4147,11 @@
       </c>
     </row>
     <row r="11" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
       <c r="D11" s="4" t="s">
         <v>42</v>
       </c>
@@ -4181,11 +4181,11 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
       <c r="D12" s="4" t="s">
         <v>46</v>
       </c>
@@ -4215,11 +4215,11 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
       <c r="D13" s="4" t="s">
         <v>49</v>
       </c>
@@ -4249,11 +4249,11 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
       <c r="D14" s="4" t="s">
         <v>53</v>
       </c>
@@ -4283,11 +4283,11 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
       <c r="D15" s="4" t="s">
         <v>58</v>
       </c>
@@ -4317,11 +4317,11 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
       <c r="D16" s="4" t="s">
         <v>61</v>
       </c>
@@ -4351,11 +4351,11 @@
       </c>
     </row>
     <row r="17" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
       <c r="D17" s="4" t="s">
         <v>64</v>
       </c>
@@ -4385,11 +4385,11 @@
       </c>
     </row>
     <row r="18" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
       <c r="D18" s="4" t="s">
         <v>68</v>
       </c>
@@ -4419,11 +4419,11 @@
       </c>
     </row>
     <row r="19" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
       <c r="D19" s="4" t="s">
         <v>71</v>
       </c>
@@ -4453,11 +4453,11 @@
       </c>
     </row>
     <row r="20" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="9" t="s">
+      <c r="A20" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
       <c r="D20" s="4" t="s">
         <v>75</v>
       </c>
@@ -4487,11 +4487,11 @@
       </c>
     </row>
     <row r="21" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
       <c r="D21" s="4" t="s">
         <v>79</v>
       </c>
@@ -4521,11 +4521,11 @@
       </c>
     </row>
     <row r="22" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
       <c r="D22" s="4" t="s">
         <v>83</v>
       </c>
@@ -4555,11 +4555,11 @@
       </c>
     </row>
     <row r="23" spans="1:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="9" t="s">
+      <c r="A23" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
       <c r="D23" s="4" t="s">
         <v>87</v>
       </c>
@@ -4589,11 +4589,11 @@
       </c>
     </row>
     <row r="24" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="9" t="s">
+      <c r="A24" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
       <c r="D24" s="4" t="s">
         <v>91</v>
       </c>
@@ -4623,11 +4623,11 @@
       </c>
     </row>
     <row r="25" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="9" t="s">
+      <c r="A25" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
       <c r="D25" s="4" t="s">
         <v>95</v>
       </c>
@@ -4657,11 +4657,11 @@
       </c>
     </row>
     <row r="26" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="9" t="s">
+      <c r="A26" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
       <c r="D26" s="4" t="s">
         <v>98</v>
       </c>
@@ -4691,11 +4691,11 @@
       </c>
     </row>
     <row r="27" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="9" t="s">
+      <c r="A27" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
       <c r="D27" s="4" t="s">
         <v>102</v>
       </c>
@@ -4725,11 +4725,11 @@
       </c>
     </row>
     <row r="28" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="9" t="s">
+      <c r="A28" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
       <c r="D28" s="4" t="s">
         <v>107</v>
       </c>
@@ -4759,11 +4759,11 @@
       </c>
     </row>
     <row r="29" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="9" t="s">
+      <c r="A29" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
       <c r="D29" s="4" t="s">
         <v>110</v>
       </c>
@@ -4793,11 +4793,11 @@
       </c>
     </row>
     <row r="30" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="9" t="s">
+      <c r="A30" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
       <c r="D30" s="4" t="s">
         <v>114</v>
       </c>
@@ -4827,11 +4827,11 @@
       </c>
     </row>
     <row r="31" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="9" t="s">
+      <c r="A31" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
       <c r="D31" s="4" t="s">
         <v>118</v>
       </c>
@@ -4861,11 +4861,11 @@
       </c>
     </row>
     <row r="32" spans="1:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="9" t="s">
+      <c r="A32" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
       <c r="D32" s="4" t="s">
         <v>123</v>
       </c>
@@ -4895,11 +4895,11 @@
       </c>
     </row>
     <row r="33" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="9" t="s">
+      <c r="A33" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
       <c r="D33" s="4" t="s">
         <v>126</v>
       </c>
@@ -4929,11 +4929,11 @@
       </c>
     </row>
     <row r="34" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="9" t="s">
+      <c r="A34" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
       <c r="D34" s="4" t="s">
         <v>130</v>
       </c>
@@ -4963,11 +4963,11 @@
       </c>
     </row>
     <row r="35" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="9" t="s">
+      <c r="A35" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
       <c r="D35" s="4" t="s">
         <v>134</v>
       </c>
@@ -4997,11 +4997,11 @@
       </c>
     </row>
     <row r="36" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="9" t="s">
+      <c r="A36" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
       <c r="D36" s="4" t="s">
         <v>140</v>
       </c>
@@ -5031,11 +5031,11 @@
       </c>
     </row>
     <row r="37" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="9" t="s">
+      <c r="A37" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
+      <c r="B37" s="8"/>
+      <c r="C37" s="8"/>
       <c r="D37" s="4" t="s">
         <v>144</v>
       </c>
@@ -5065,11 +5065,11 @@
       </c>
     </row>
     <row r="38" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="9" t="s">
+      <c r="A38" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
       <c r="D38" s="4" t="s">
         <v>147</v>
       </c>
@@ -5099,11 +5099,11 @@
       </c>
     </row>
     <row r="39" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="9" t="s">
+      <c r="A39" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
       <c r="D39" s="4" t="s">
         <v>150</v>
       </c>
@@ -5133,11 +5133,11 @@
       </c>
     </row>
     <row r="40" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="9" t="s">
+      <c r="A40" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="B40" s="9"/>
-      <c r="C40" s="9"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
       <c r="D40" s="4" t="s">
         <v>154</v>
       </c>
@@ -5167,11 +5167,11 @@
       </c>
     </row>
     <row r="41" spans="1:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="9" t="s">
+      <c r="A41" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
+      <c r="B41" s="8"/>
+      <c r="C41" s="8"/>
       <c r="D41" s="4" t="s">
         <v>160</v>
       </c>
@@ -5201,11 +5201,11 @@
       </c>
     </row>
     <row r="42" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="9" t="s">
+      <c r="A42" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
+      <c r="B42" s="8"/>
+      <c r="C42" s="8"/>
       <c r="D42" s="4" t="s">
         <v>164</v>
       </c>
@@ -5235,11 +5235,11 @@
       </c>
     </row>
     <row r="43" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="9" t="s">
+      <c r="A43" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="B43" s="9"/>
-      <c r="C43" s="9"/>
+      <c r="B43" s="8"/>
+      <c r="C43" s="8"/>
       <c r="D43" s="4" t="s">
         <v>167</v>
       </c>
@@ -5269,11 +5269,11 @@
       </c>
     </row>
     <row r="44" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="9" t="s">
+      <c r="A44" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
+      <c r="B44" s="8"/>
+      <c r="C44" s="8"/>
       <c r="D44" s="4" t="s">
         <v>171</v>
       </c>
@@ -5303,11 +5303,11 @@
       </c>
     </row>
     <row r="45" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="9" t="s">
+      <c r="A45" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
+      <c r="B45" s="8"/>
+      <c r="C45" s="8"/>
       <c r="D45" s="4" t="s">
         <v>175</v>
       </c>
@@ -5337,11 +5337,11 @@
       </c>
     </row>
     <row r="46" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="9" t="s">
+      <c r="A46" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="B46" s="9"/>
-      <c r="C46" s="9"/>
+      <c r="B46" s="8"/>
+      <c r="C46" s="8"/>
       <c r="D46" s="4" t="s">
         <v>179</v>
       </c>
@@ -5371,11 +5371,11 @@
       </c>
     </row>
     <row r="47" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="9" t="s">
+      <c r="A47" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="B47" s="9"/>
-      <c r="C47" s="9"/>
+      <c r="B47" s="8"/>
+      <c r="C47" s="8"/>
       <c r="D47" s="4" t="s">
         <v>183</v>
       </c>
@@ -5405,11 +5405,11 @@
       </c>
     </row>
     <row r="48" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="9" t="s">
+      <c r="A48" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="B48" s="9"/>
-      <c r="C48" s="9"/>
+      <c r="B48" s="8"/>
+      <c r="C48" s="8"/>
       <c r="D48" s="4" t="s">
         <v>187</v>
       </c>
@@ -5439,11 +5439,11 @@
       </c>
     </row>
     <row r="49" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="9" t="s">
+      <c r="A49" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="B49" s="9"/>
-      <c r="C49" s="9"/>
+      <c r="B49" s="8"/>
+      <c r="C49" s="8"/>
       <c r="D49" s="4" t="s">
         <v>191</v>
       </c>
@@ -5473,11 +5473,11 @@
       </c>
     </row>
     <row r="50" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="9" t="s">
+      <c r="A50" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="B50" s="9"/>
-      <c r="C50" s="9"/>
+      <c r="B50" s="8"/>
+      <c r="C50" s="8"/>
       <c r="D50" s="4" t="s">
         <v>195</v>
       </c>
@@ -5507,11 +5507,11 @@
       </c>
     </row>
     <row r="51" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="9" t="s">
+      <c r="A51" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="B51" s="9"/>
-      <c r="C51" s="9"/>
+      <c r="B51" s="8"/>
+      <c r="C51" s="8"/>
       <c r="D51" s="4" t="s">
         <v>198</v>
       </c>
@@ -5541,11 +5541,11 @@
       </c>
     </row>
     <row r="52" spans="1:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="9" t="s">
+      <c r="A52" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="B52" s="9"/>
-      <c r="C52" s="9"/>
+      <c r="B52" s="8"/>
+      <c r="C52" s="8"/>
       <c r="D52" s="4" t="s">
         <v>202</v>
       </c>
@@ -5575,11 +5575,11 @@
       </c>
     </row>
     <row r="53" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="9" t="s">
+      <c r="A53" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="B53" s="9"/>
-      <c r="C53" s="9"/>
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
       <c r="D53" s="4" t="s">
         <v>205</v>
       </c>
@@ -5609,11 +5609,11 @@
       </c>
     </row>
     <row r="54" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="9" t="s">
+      <c r="A54" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="B54" s="9"/>
-      <c r="C54" s="9"/>
+      <c r="B54" s="8"/>
+      <c r="C54" s="8"/>
       <c r="D54" s="4" t="s">
         <v>208</v>
       </c>
@@ -5643,11 +5643,11 @@
       </c>
     </row>
     <row r="55" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="9" t="s">
+      <c r="A55" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="B55" s="9"/>
-      <c r="C55" s="9"/>
+      <c r="B55" s="8"/>
+      <c r="C55" s="8"/>
       <c r="D55" s="4" t="s">
         <v>212</v>
       </c>
@@ -5677,11 +5677,11 @@
       </c>
     </row>
     <row r="56" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="9" t="s">
+      <c r="A56" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="B56" s="9"/>
-      <c r="C56" s="9"/>
+      <c r="B56" s="8"/>
+      <c r="C56" s="8"/>
       <c r="D56" s="4" t="s">
         <v>215</v>
       </c>
@@ -5711,11 +5711,11 @@
       </c>
     </row>
     <row r="57" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="9" t="s">
+      <c r="A57" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="B57" s="9"/>
-      <c r="C57" s="9"/>
+      <c r="B57" s="8"/>
+      <c r="C57" s="8"/>
       <c r="D57" s="4" t="s">
         <v>219</v>
       </c>
@@ -5745,11 +5745,11 @@
       </c>
     </row>
     <row r="58" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="9" t="s">
+      <c r="A58" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="B58" s="9"/>
-      <c r="C58" s="9"/>
+      <c r="B58" s="8"/>
+      <c r="C58" s="8"/>
       <c r="D58" s="4" t="s">
         <v>224</v>
       </c>
@@ -5779,11 +5779,11 @@
       </c>
     </row>
     <row r="59" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="9" t="s">
+      <c r="A59" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="B59" s="9"/>
-      <c r="C59" s="9"/>
+      <c r="B59" s="8"/>
+      <c r="C59" s="8"/>
       <c r="D59" s="4" t="s">
         <v>227</v>
       </c>
@@ -5813,11 +5813,11 @@
       </c>
     </row>
     <row r="60" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="9" t="s">
+      <c r="A60" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="B60" s="9"/>
-      <c r="C60" s="9"/>
+      <c r="B60" s="8"/>
+      <c r="C60" s="8"/>
       <c r="D60" s="4" t="s">
         <v>231</v>
       </c>
@@ -5847,11 +5847,11 @@
       </c>
     </row>
     <row r="61" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="9" t="s">
+      <c r="A61" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="B61" s="9"/>
-      <c r="C61" s="9"/>
+      <c r="B61" s="8"/>
+      <c r="C61" s="8"/>
       <c r="D61" s="4" t="s">
         <v>236</v>
       </c>
@@ -5881,11 +5881,11 @@
       </c>
     </row>
     <row r="62" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="9" t="s">
+      <c r="A62" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="B62" s="9"/>
-      <c r="C62" s="9"/>
+      <c r="B62" s="8"/>
+      <c r="C62" s="8"/>
       <c r="D62" s="4" t="s">
         <v>240</v>
       </c>
@@ -5915,11 +5915,11 @@
       </c>
     </row>
     <row r="63" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="9" t="s">
+      <c r="A63" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="B63" s="9"/>
-      <c r="C63" s="9"/>
+      <c r="B63" s="8"/>
+      <c r="C63" s="8"/>
       <c r="D63" s="4" t="s">
         <v>243</v>
       </c>
@@ -5949,11 +5949,11 @@
       </c>
     </row>
     <row r="64" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="9" t="s">
+      <c r="A64" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="B64" s="9"/>
-      <c r="C64" s="9"/>
+      <c r="B64" s="8"/>
+      <c r="C64" s="8"/>
       <c r="D64" s="4" t="s">
         <v>246</v>
       </c>
@@ -5983,11 +5983,11 @@
       </c>
     </row>
     <row r="65" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="9" t="s">
+      <c r="A65" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="B65" s="9"/>
-      <c r="C65" s="9"/>
+      <c r="B65" s="8"/>
+      <c r="C65" s="8"/>
       <c r="D65" s="4" t="s">
         <v>250</v>
       </c>
@@ -6017,11 +6017,11 @@
       </c>
     </row>
     <row r="66" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="9" t="s">
+      <c r="A66" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="B66" s="9"/>
-      <c r="C66" s="9"/>
+      <c r="B66" s="8"/>
+      <c r="C66" s="8"/>
       <c r="D66" s="4" t="s">
         <v>254</v>
       </c>
@@ -6051,11 +6051,11 @@
       </c>
     </row>
     <row r="67" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="9" t="s">
+      <c r="A67" s="8" t="s">
         <v>257</v>
       </c>
-      <c r="B67" s="9"/>
-      <c r="C67" s="9"/>
+      <c r="B67" s="8"/>
+      <c r="C67" s="8"/>
       <c r="D67" s="4" t="s">
         <v>257</v>
       </c>
@@ -6085,11 +6085,11 @@
       </c>
     </row>
     <row r="68" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="9" t="s">
+      <c r="A68" s="8" t="s">
         <v>260</v>
       </c>
-      <c r="B68" s="9"/>
-      <c r="C68" s="9"/>
+      <c r="B68" s="8"/>
+      <c r="C68" s="8"/>
       <c r="D68" s="4" t="s">
         <v>260</v>
       </c>
@@ -6119,11 +6119,11 @@
       </c>
     </row>
     <row r="69" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="9" t="s">
+      <c r="A69" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="B69" s="9"/>
-      <c r="C69" s="9"/>
+      <c r="B69" s="8"/>
+      <c r="C69" s="8"/>
       <c r="D69" s="4" t="s">
         <v>264</v>
       </c>
@@ -6153,11 +6153,11 @@
       </c>
     </row>
     <row r="70" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="9" t="s">
+      <c r="A70" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="B70" s="9"/>
-      <c r="C70" s="9"/>
+      <c r="B70" s="8"/>
+      <c r="C70" s="8"/>
       <c r="D70" s="4" t="s">
         <v>267</v>
       </c>
@@ -6187,11 +6187,11 @@
       </c>
     </row>
     <row r="71" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="9" t="s">
+      <c r="A71" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="B71" s="9"/>
-      <c r="C71" s="9"/>
+      <c r="B71" s="8"/>
+      <c r="C71" s="8"/>
       <c r="D71" s="4" t="s">
         <v>271</v>
       </c>
@@ -6221,11 +6221,11 @@
       </c>
     </row>
     <row r="72" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="9" t="s">
+      <c r="A72" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="B72" s="9"/>
-      <c r="C72" s="9"/>
+      <c r="B72" s="8"/>
+      <c r="C72" s="8"/>
       <c r="D72" s="4" t="s">
         <v>274</v>
       </c>
@@ -6255,11 +6255,11 @@
       </c>
     </row>
     <row r="73" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="9" t="s">
+      <c r="A73" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="B73" s="9"/>
-      <c r="C73" s="9"/>
+      <c r="B73" s="8"/>
+      <c r="C73" s="8"/>
       <c r="D73" s="4" t="s">
         <v>278</v>
       </c>
@@ -6289,11 +6289,11 @@
       </c>
     </row>
     <row r="74" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="9" t="s">
+      <c r="A74" s="8" t="s">
         <v>281</v>
       </c>
-      <c r="B74" s="9"/>
-      <c r="C74" s="9"/>
+      <c r="B74" s="8"/>
+      <c r="C74" s="8"/>
       <c r="D74" s="4" t="s">
         <v>282</v>
       </c>
@@ -6323,11 +6323,11 @@
       </c>
     </row>
     <row r="75" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="9" t="s">
+      <c r="A75" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="B75" s="9"/>
-      <c r="C75" s="9"/>
+      <c r="B75" s="8"/>
+      <c r="C75" s="8"/>
       <c r="D75" s="4" t="s">
         <v>286</v>
       </c>
@@ -6357,11 +6357,11 @@
       </c>
     </row>
     <row r="76" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="9" t="s">
+      <c r="A76" s="8" t="s">
         <v>289</v>
       </c>
-      <c r="B76" s="9"/>
-      <c r="C76" s="9"/>
+      <c r="B76" s="8"/>
+      <c r="C76" s="8"/>
       <c r="D76" s="4" t="s">
         <v>290</v>
       </c>
@@ -6391,11 +6391,11 @@
       </c>
     </row>
     <row r="77" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="9" t="s">
+      <c r="A77" s="8" t="s">
         <v>293</v>
       </c>
-      <c r="B77" s="9"/>
-      <c r="C77" s="9"/>
+      <c r="B77" s="8"/>
+      <c r="C77" s="8"/>
       <c r="D77" s="4" t="s">
         <v>294</v>
       </c>
@@ -6425,11 +6425,11 @@
       </c>
     </row>
     <row r="78" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="9" t="s">
+      <c r="A78" s="8" t="s">
         <v>297</v>
       </c>
-      <c r="B78" s="9"/>
-      <c r="C78" s="9"/>
+      <c r="B78" s="8"/>
+      <c r="C78" s="8"/>
       <c r="D78" s="4" t="s">
         <v>298</v>
       </c>
@@ -6459,11 +6459,11 @@
       </c>
     </row>
     <row r="79" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="9" t="s">
+      <c r="A79" s="8" t="s">
         <v>297</v>
       </c>
-      <c r="B79" s="9"/>
-      <c r="C79" s="9"/>
+      <c r="B79" s="8"/>
+      <c r="C79" s="8"/>
       <c r="D79" s="4" t="s">
         <v>302</v>
       </c>
@@ -6489,15 +6489,15 @@
         <v>223</v>
       </c>
       <c r="L79">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="9" t="s">
+      <c r="A80" s="8" t="s">
         <v>305</v>
       </c>
-      <c r="B80" s="9"/>
-      <c r="C80" s="9"/>
+      <c r="B80" s="8"/>
+      <c r="C80" s="8"/>
       <c r="D80" s="4" t="s">
         <v>306</v>
       </c>
@@ -6527,11 +6527,11 @@
       </c>
     </row>
     <row r="81" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="9" t="s">
+      <c r="A81" s="8" t="s">
         <v>309</v>
       </c>
-      <c r="B81" s="9"/>
-      <c r="C81" s="9"/>
+      <c r="B81" s="8"/>
+      <c r="C81" s="8"/>
       <c r="D81" s="4" t="s">
         <v>310</v>
       </c>
@@ -6561,11 +6561,11 @@
       </c>
     </row>
     <row r="82" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="9" t="s">
+      <c r="A82" s="8" t="s">
         <v>309</v>
       </c>
-      <c r="B82" s="9"/>
-      <c r="C82" s="9"/>
+      <c r="B82" s="8"/>
+      <c r="C82" s="8"/>
       <c r="D82" s="4" t="s">
         <v>313</v>
       </c>
@@ -6595,11 +6595,11 @@
       </c>
     </row>
     <row r="83" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="9" t="s">
+      <c r="A83" s="8" t="s">
         <v>316</v>
       </c>
-      <c r="B83" s="9"/>
-      <c r="C83" s="9"/>
+      <c r="B83" s="8"/>
+      <c r="C83" s="8"/>
       <c r="D83" s="4" t="s">
         <v>317</v>
       </c>
@@ -6629,11 +6629,11 @@
       </c>
     </row>
     <row r="84" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="9" t="s">
+      <c r="A84" s="8" t="s">
         <v>321</v>
       </c>
-      <c r="B84" s="9"/>
-      <c r="C84" s="9"/>
+      <c r="B84" s="8"/>
+      <c r="C84" s="8"/>
       <c r="D84" s="4" t="s">
         <v>321</v>
       </c>
@@ -6663,11 +6663,11 @@
       </c>
     </row>
     <row r="85" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="9" t="s">
+      <c r="A85" s="8" t="s">
         <v>324</v>
       </c>
-      <c r="B85" s="9"/>
-      <c r="C85" s="9"/>
+      <c r="B85" s="8"/>
+      <c r="C85" s="8"/>
       <c r="D85" s="4" t="s">
         <v>325</v>
       </c>
@@ -6697,11 +6697,11 @@
       </c>
     </row>
     <row r="86" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="9" t="s">
+      <c r="A86" s="8" t="s">
         <v>324</v>
       </c>
-      <c r="B86" s="9"/>
-      <c r="C86" s="9"/>
+      <c r="B86" s="8"/>
+      <c r="C86" s="8"/>
       <c r="D86" s="4" t="s">
         <v>328</v>
       </c>
@@ -6731,11 +6731,11 @@
       </c>
     </row>
     <row r="87" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="9" t="s">
+      <c r="A87" s="8" t="s">
         <v>331</v>
       </c>
-      <c r="B87" s="9"/>
-      <c r="C87" s="9"/>
+      <c r="B87" s="8"/>
+      <c r="C87" s="8"/>
       <c r="D87" s="4" t="s">
         <v>332</v>
       </c>
@@ -6765,11 +6765,11 @@
       </c>
     </row>
     <row r="88" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="9" t="s">
+      <c r="A88" s="8" t="s">
         <v>335</v>
       </c>
-      <c r="B88" s="9"/>
-      <c r="C88" s="9"/>
+      <c r="B88" s="8"/>
+      <c r="C88" s="8"/>
       <c r="D88" s="4" t="s">
         <v>336</v>
       </c>
@@ -6799,11 +6799,11 @@
       </c>
     </row>
     <row r="89" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="9" t="s">
+      <c r="A89" s="8" t="s">
         <v>335</v>
       </c>
-      <c r="B89" s="9"/>
-      <c r="C89" s="9"/>
+      <c r="B89" s="8"/>
+      <c r="C89" s="8"/>
       <c r="D89" s="4" t="s">
         <v>339</v>
       </c>
@@ -6833,11 +6833,11 @@
       </c>
     </row>
     <row r="90" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="9" t="s">
+      <c r="A90" s="8" t="s">
         <v>341</v>
       </c>
-      <c r="B90" s="9"/>
-      <c r="C90" s="9"/>
+      <c r="B90" s="8"/>
+      <c r="C90" s="8"/>
       <c r="D90" s="4" t="s">
         <v>342</v>
       </c>
@@ -6867,11 +6867,11 @@
       </c>
     </row>
     <row r="91" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="9" t="s">
+      <c r="A91" s="8" t="s">
         <v>345</v>
       </c>
-      <c r="B91" s="9"/>
-      <c r="C91" s="9"/>
+      <c r="B91" s="8"/>
+      <c r="C91" s="8"/>
       <c r="D91" s="4" t="s">
         <v>346</v>
       </c>
@@ -6901,11 +6901,11 @@
       </c>
     </row>
     <row r="92" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="9" t="s">
+      <c r="A92" s="8" t="s">
         <v>349</v>
       </c>
-      <c r="B92" s="9"/>
-      <c r="C92" s="9"/>
+      <c r="B92" s="8"/>
+      <c r="C92" s="8"/>
       <c r="D92" s="4" t="s">
         <v>350</v>
       </c>
@@ -6935,11 +6935,11 @@
       </c>
     </row>
     <row r="93" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="9" t="s">
+      <c r="A93" s="8" t="s">
         <v>353</v>
       </c>
-      <c r="B93" s="9"/>
-      <c r="C93" s="9"/>
+      <c r="B93" s="8"/>
+      <c r="C93" s="8"/>
       <c r="D93" s="4" t="s">
         <v>354</v>
       </c>
@@ -6969,11 +6969,11 @@
       </c>
     </row>
     <row r="94" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="9" t="s">
+      <c r="A94" s="8" t="s">
         <v>358</v>
       </c>
-      <c r="B94" s="9"/>
-      <c r="C94" s="9"/>
+      <c r="B94" s="8"/>
+      <c r="C94" s="8"/>
       <c r="D94" s="4" t="s">
         <v>359</v>
       </c>
@@ -7003,11 +7003,11 @@
       </c>
     </row>
     <row r="95" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="9" t="s">
+      <c r="A95" s="8" t="s">
         <v>362</v>
       </c>
-      <c r="B95" s="9"/>
-      <c r="C95" s="9"/>
+      <c r="B95" s="8"/>
+      <c r="C95" s="8"/>
       <c r="D95" s="4" t="s">
         <v>363</v>
       </c>
@@ -7037,11 +7037,11 @@
       </c>
     </row>
     <row r="96" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="9" t="s">
+      <c r="A96" s="8" t="s">
         <v>367</v>
       </c>
-      <c r="B96" s="9"/>
-      <c r="C96" s="9"/>
+      <c r="B96" s="8"/>
+      <c r="C96" s="8"/>
       <c r="D96" s="4" t="s">
         <v>368</v>
       </c>
@@ -7071,11 +7071,11 @@
       </c>
     </row>
     <row r="97" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="9" t="s">
+      <c r="A97" s="8" t="s">
         <v>372</v>
       </c>
-      <c r="B97" s="9"/>
-      <c r="C97" s="9"/>
+      <c r="B97" s="8"/>
+      <c r="C97" s="8"/>
       <c r="D97" s="4" t="s">
         <v>373</v>
       </c>
@@ -7105,11 +7105,11 @@
       </c>
     </row>
     <row r="98" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="9" t="s">
+      <c r="A98" s="8" t="s">
         <v>376</v>
       </c>
-      <c r="B98" s="9"/>
-      <c r="C98" s="9"/>
+      <c r="B98" s="8"/>
+      <c r="C98" s="8"/>
       <c r="D98" s="4" t="s">
         <v>376</v>
       </c>
@@ -7139,11 +7139,11 @@
       </c>
     </row>
     <row r="99" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="9" t="s">
+      <c r="A99" s="8" t="s">
         <v>379</v>
       </c>
-      <c r="B99" s="9"/>
-      <c r="C99" s="9"/>
+      <c r="B99" s="8"/>
+      <c r="C99" s="8"/>
       <c r="D99" s="4" t="s">
         <v>380</v>
       </c>
@@ -7173,11 +7173,11 @@
       </c>
     </row>
     <row r="100" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="9" t="s">
+      <c r="A100" s="8" t="s">
         <v>383</v>
       </c>
-      <c r="B100" s="9"/>
-      <c r="C100" s="9"/>
+      <c r="B100" s="8"/>
+      <c r="C100" s="8"/>
       <c r="D100" s="4" t="s">
         <v>384</v>
       </c>
@@ -7207,11 +7207,11 @@
       </c>
     </row>
     <row r="101" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="9" t="s">
+      <c r="A101" s="8" t="s">
         <v>387</v>
       </c>
-      <c r="B101" s="9"/>
-      <c r="C101" s="9"/>
+      <c r="B101" s="8"/>
+      <c r="C101" s="8"/>
       <c r="D101" s="4" t="s">
         <v>388</v>
       </c>
@@ -7241,11 +7241,11 @@
       </c>
     </row>
     <row r="102" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="9" t="s">
+      <c r="A102" s="8" t="s">
         <v>391</v>
       </c>
-      <c r="B102" s="9"/>
-      <c r="C102" s="9"/>
+      <c r="B102" s="8"/>
+      <c r="C102" s="8"/>
       <c r="D102" s="4" t="s">
         <v>392</v>
       </c>
@@ -7275,11 +7275,11 @@
       </c>
     </row>
     <row r="103" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="9" t="s">
+      <c r="A103" s="8" t="s">
         <v>395</v>
       </c>
-      <c r="B103" s="9"/>
-      <c r="C103" s="9"/>
+      <c r="B103" s="8"/>
+      <c r="C103" s="8"/>
       <c r="D103" s="4" t="s">
         <v>395</v>
       </c>
@@ -7309,11 +7309,11 @@
       </c>
     </row>
     <row r="104" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="9" t="s">
+      <c r="A104" s="8" t="s">
         <v>398</v>
       </c>
-      <c r="B104" s="9"/>
-      <c r="C104" s="9"/>
+      <c r="B104" s="8"/>
+      <c r="C104" s="8"/>
       <c r="D104" s="4" t="s">
         <v>399</v>
       </c>
@@ -7343,11 +7343,11 @@
       </c>
     </row>
     <row r="105" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="9" t="s">
+      <c r="A105" s="8" t="s">
         <v>402</v>
       </c>
-      <c r="B105" s="9"/>
-      <c r="C105" s="9"/>
+      <c r="B105" s="8"/>
+      <c r="C105" s="8"/>
       <c r="D105" s="4" t="s">
         <v>403</v>
       </c>
@@ -7377,11 +7377,11 @@
       </c>
     </row>
     <row r="106" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A106" s="9" t="s">
+      <c r="A106" s="8" t="s">
         <v>402</v>
       </c>
-      <c r="B106" s="9"/>
-      <c r="C106" s="9"/>
+      <c r="B106" s="8"/>
+      <c r="C106" s="8"/>
       <c r="D106" s="4" t="s">
         <v>406</v>
       </c>
@@ -7411,11 +7411,11 @@
       </c>
     </row>
     <row r="107" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="9" t="s">
+      <c r="A107" s="8" t="s">
         <v>409</v>
       </c>
-      <c r="B107" s="9"/>
-      <c r="C107" s="9"/>
+      <c r="B107" s="8"/>
+      <c r="C107" s="8"/>
       <c r="D107" s="4" t="s">
         <v>410</v>
       </c>
@@ -7445,11 +7445,11 @@
       </c>
     </row>
     <row r="108" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="9" t="s">
+      <c r="A108" s="8" t="s">
         <v>409</v>
       </c>
-      <c r="B108" s="9"/>
-      <c r="C108" s="9"/>
+      <c r="B108" s="8"/>
+      <c r="C108" s="8"/>
       <c r="D108" s="4" t="s">
         <v>410</v>
       </c>
@@ -7479,11 +7479,11 @@
       </c>
     </row>
     <row r="109" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="9" t="s">
+      <c r="A109" s="8" t="s">
         <v>414</v>
       </c>
-      <c r="B109" s="9"/>
-      <c r="C109" s="9"/>
+      <c r="B109" s="8"/>
+      <c r="C109" s="8"/>
       <c r="D109" s="4" t="s">
         <v>415</v>
       </c>
@@ -7513,11 +7513,11 @@
       </c>
     </row>
     <row r="110" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="9" t="s">
+      <c r="A110" s="8" t="s">
         <v>414</v>
       </c>
-      <c r="B110" s="9"/>
-      <c r="C110" s="9"/>
+      <c r="B110" s="8"/>
+      <c r="C110" s="8"/>
       <c r="D110" s="4" t="s">
         <v>418</v>
       </c>
@@ -7547,11 +7547,11 @@
       </c>
     </row>
     <row r="111" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="9" t="s">
+      <c r="A111" s="8" t="s">
         <v>420</v>
       </c>
-      <c r="B111" s="9"/>
-      <c r="C111" s="9"/>
+      <c r="B111" s="8"/>
+      <c r="C111" s="8"/>
       <c r="D111" s="4" t="s">
         <v>420</v>
       </c>
@@ -7581,11 +7581,11 @@
       </c>
     </row>
     <row r="112" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="9" t="s">
+      <c r="A112" s="8" t="s">
         <v>423</v>
       </c>
-      <c r="B112" s="9"/>
-      <c r="C112" s="9"/>
+      <c r="B112" s="8"/>
+      <c r="C112" s="8"/>
       <c r="D112" s="4" t="s">
         <v>423</v>
       </c>
@@ -7615,11 +7615,11 @@
       </c>
     </row>
     <row r="113" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="9" t="s">
+      <c r="A113" s="8" t="s">
         <v>426</v>
       </c>
-      <c r="B113" s="9"/>
-      <c r="C113" s="9"/>
+      <c r="B113" s="8"/>
+      <c r="C113" s="8"/>
       <c r="D113" s="4" t="s">
         <v>426</v>
       </c>
@@ -7649,11 +7649,11 @@
       </c>
     </row>
     <row r="114" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="9" t="s">
+      <c r="A114" s="8" t="s">
         <v>429</v>
       </c>
-      <c r="B114" s="9"/>
-      <c r="C114" s="9"/>
+      <c r="B114" s="8"/>
+      <c r="C114" s="8"/>
       <c r="D114" s="4" t="s">
         <v>430</v>
       </c>
@@ -7683,11 +7683,11 @@
       </c>
     </row>
     <row r="115" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="9" t="s">
+      <c r="A115" s="8" t="s">
         <v>433</v>
       </c>
-      <c r="B115" s="9"/>
-      <c r="C115" s="9"/>
+      <c r="B115" s="8"/>
+      <c r="C115" s="8"/>
       <c r="D115" s="4" t="s">
         <v>434</v>
       </c>
@@ -7717,11 +7717,11 @@
       </c>
     </row>
     <row r="116" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A116" s="9" t="s">
+      <c r="A116" s="8" t="s">
         <v>433</v>
       </c>
-      <c r="B116" s="9"/>
-      <c r="C116" s="9"/>
+      <c r="B116" s="8"/>
+      <c r="C116" s="8"/>
       <c r="D116" s="4" t="s">
         <v>437</v>
       </c>
@@ -7751,11 +7751,11 @@
       </c>
     </row>
     <row r="117" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A117" s="9" t="s">
+      <c r="A117" s="8" t="s">
         <v>441</v>
       </c>
-      <c r="B117" s="9"/>
-      <c r="C117" s="9"/>
+      <c r="B117" s="8"/>
+      <c r="C117" s="8"/>
       <c r="D117" s="4" t="s">
         <v>441</v>
       </c>
@@ -7785,11 +7785,11 @@
       </c>
     </row>
     <row r="118" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A118" s="9" t="s">
+      <c r="A118" s="8" t="s">
         <v>444</v>
       </c>
-      <c r="B118" s="9"/>
-      <c r="C118" s="9"/>
+      <c r="B118" s="8"/>
+      <c r="C118" s="8"/>
       <c r="D118" s="4" t="s">
         <v>444</v>
       </c>
@@ -7819,11 +7819,11 @@
       </c>
     </row>
     <row r="119" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A119" s="9" t="s">
+      <c r="A119" s="8" t="s">
         <v>447</v>
       </c>
-      <c r="B119" s="9"/>
-      <c r="C119" s="9"/>
+      <c r="B119" s="8"/>
+      <c r="C119" s="8"/>
       <c r="D119" s="4" t="s">
         <v>447</v>
       </c>
@@ -7853,11 +7853,11 @@
       </c>
     </row>
     <row r="120" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A120" s="9" t="s">
+      <c r="A120" s="8" t="s">
         <v>450</v>
       </c>
-      <c r="B120" s="9"/>
-      <c r="C120" s="9"/>
+      <c r="B120" s="8"/>
+      <c r="C120" s="8"/>
       <c r="D120" s="4" t="s">
         <v>451</v>
       </c>
@@ -7887,11 +7887,11 @@
       </c>
     </row>
     <row r="121" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="9" t="s">
+      <c r="A121" s="8" t="s">
         <v>454</v>
       </c>
-      <c r="B121" s="9"/>
-      <c r="C121" s="9"/>
+      <c r="B121" s="8"/>
+      <c r="C121" s="8"/>
       <c r="D121" s="4" t="s">
         <v>454</v>
       </c>
@@ -7921,11 +7921,11 @@
       </c>
     </row>
     <row r="122" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="9" t="s">
+      <c r="A122" s="8" t="s">
         <v>457</v>
       </c>
-      <c r="B122" s="9"/>
-      <c r="C122" s="9"/>
+      <c r="B122" s="8"/>
+      <c r="C122" s="8"/>
       <c r="D122" s="4" t="s">
         <v>458</v>
       </c>
@@ -7955,11 +7955,11 @@
       </c>
     </row>
     <row r="123" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="9" t="s">
+      <c r="A123" s="8" t="s">
         <v>461</v>
       </c>
-      <c r="B123" s="9"/>
-      <c r="C123" s="9"/>
+      <c r="B123" s="8"/>
+      <c r="C123" s="8"/>
       <c r="D123" s="4" t="s">
         <v>461</v>
       </c>
@@ -7989,11 +7989,11 @@
       </c>
     </row>
     <row r="124" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="9" t="s">
+      <c r="A124" s="8" t="s">
         <v>464</v>
       </c>
-      <c r="B124" s="9"/>
-      <c r="C124" s="9"/>
+      <c r="B124" s="8"/>
+      <c r="C124" s="8"/>
       <c r="D124" s="4" t="s">
         <v>465</v>
       </c>
@@ -8023,11 +8023,11 @@
       </c>
     </row>
     <row r="125" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A125" s="9" t="s">
+      <c r="A125" s="8" t="s">
         <v>464</v>
       </c>
-      <c r="B125" s="9"/>
-      <c r="C125" s="9"/>
+      <c r="B125" s="8"/>
+      <c r="C125" s="8"/>
       <c r="D125" s="4" t="s">
         <v>468</v>
       </c>
@@ -8057,11 +8057,11 @@
       </c>
     </row>
     <row r="126" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A126" s="9" t="s">
+      <c r="A126" s="8" t="s">
         <v>471</v>
       </c>
-      <c r="B126" s="9"/>
-      <c r="C126" s="9"/>
+      <c r="B126" s="8"/>
+      <c r="C126" s="8"/>
       <c r="D126" s="4" t="s">
         <v>472</v>
       </c>
@@ -8091,11 +8091,11 @@
       </c>
     </row>
     <row r="127" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A127" s="9" t="s">
+      <c r="A127" s="8" t="s">
         <v>471</v>
       </c>
-      <c r="B127" s="9"/>
-      <c r="C127" s="9"/>
+      <c r="B127" s="8"/>
+      <c r="C127" s="8"/>
       <c r="D127" s="4" t="s">
         <v>475</v>
       </c>
@@ -8125,11 +8125,11 @@
       </c>
     </row>
     <row r="128" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A128" s="9" t="s">
+      <c r="A128" s="8" t="s">
         <v>478</v>
       </c>
-      <c r="B128" s="9"/>
-      <c r="C128" s="9"/>
+      <c r="B128" s="8"/>
+      <c r="C128" s="8"/>
       <c r="D128" s="4" t="s">
         <v>478</v>
       </c>
@@ -8159,11 +8159,11 @@
       </c>
     </row>
     <row r="129" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A129" s="9" t="s">
+      <c r="A129" s="8" t="s">
         <v>478</v>
       </c>
-      <c r="B129" s="9"/>
-      <c r="C129" s="9"/>
+      <c r="B129" s="8"/>
+      <c r="C129" s="8"/>
       <c r="D129" s="4" t="s">
         <v>478</v>
       </c>
@@ -8193,11 +8193,11 @@
       </c>
     </row>
     <row r="130" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A130" s="9" t="s">
+      <c r="A130" s="8" t="s">
         <v>482</v>
       </c>
-      <c r="B130" s="9"/>
-      <c r="C130" s="9"/>
+      <c r="B130" s="8"/>
+      <c r="C130" s="8"/>
       <c r="D130" s="4" t="s">
         <v>483</v>
       </c>
@@ -8227,11 +8227,11 @@
       </c>
     </row>
     <row r="131" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A131" s="9" t="s">
+      <c r="A131" s="8" t="s">
         <v>486</v>
       </c>
-      <c r="B131" s="9"/>
-      <c r="C131" s="9"/>
+      <c r="B131" s="8"/>
+      <c r="C131" s="8"/>
       <c r="D131" s="4" t="s">
         <v>487</v>
       </c>
@@ -8261,11 +8261,11 @@
       </c>
     </row>
     <row r="132" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A132" s="9" t="s">
+      <c r="A132" s="8" t="s">
         <v>486</v>
       </c>
-      <c r="B132" s="9"/>
-      <c r="C132" s="9"/>
+      <c r="B132" s="8"/>
+      <c r="C132" s="8"/>
       <c r="D132" s="4" t="s">
         <v>490</v>
       </c>
@@ -8295,11 +8295,11 @@
       </c>
     </row>
     <row r="133" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A133" s="9" t="s">
+      <c r="A133" s="8" t="s">
         <v>493</v>
       </c>
-      <c r="B133" s="9"/>
-      <c r="C133" s="9"/>
+      <c r="B133" s="8"/>
+      <c r="C133" s="8"/>
       <c r="D133" s="4" t="s">
         <v>494</v>
       </c>
@@ -8329,11 +8329,11 @@
       </c>
     </row>
     <row r="134" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A134" s="9" t="s">
+      <c r="A134" s="8" t="s">
         <v>497</v>
       </c>
-      <c r="B134" s="9"/>
-      <c r="C134" s="9"/>
+      <c r="B134" s="8"/>
+      <c r="C134" s="8"/>
       <c r="D134" s="4" t="s">
         <v>497</v>
       </c>
@@ -8363,11 +8363,11 @@
       </c>
     </row>
     <row r="135" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A135" s="9" t="s">
+      <c r="A135" s="8" t="s">
         <v>500</v>
       </c>
-      <c r="B135" s="9"/>
-      <c r="C135" s="9"/>
+      <c r="B135" s="8"/>
+      <c r="C135" s="8"/>
       <c r="D135" s="4" t="s">
         <v>500</v>
       </c>
@@ -8397,11 +8397,11 @@
       </c>
     </row>
     <row r="136" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A136" s="9" t="s">
+      <c r="A136" s="8" t="s">
         <v>503</v>
       </c>
-      <c r="B136" s="9"/>
-      <c r="C136" s="9"/>
+      <c r="B136" s="8"/>
+      <c r="C136" s="8"/>
       <c r="D136" s="4" t="s">
         <v>503</v>
       </c>
@@ -8431,11 +8431,11 @@
       </c>
     </row>
     <row r="137" spans="1:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A137" s="9" t="s">
+      <c r="A137" s="8" t="s">
         <v>506</v>
       </c>
-      <c r="B137" s="9"/>
-      <c r="C137" s="9"/>
+      <c r="B137" s="8"/>
+      <c r="C137" s="8"/>
       <c r="D137" s="4" t="s">
         <v>507</v>
       </c>
@@ -8465,11 +8465,11 @@
       </c>
     </row>
     <row r="138" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A138" s="9" t="s">
+      <c r="A138" s="8" t="s">
         <v>511</v>
       </c>
-      <c r="B138" s="9"/>
-      <c r="C138" s="9"/>
+      <c r="B138" s="8"/>
+      <c r="C138" s="8"/>
       <c r="D138" s="4" t="s">
         <v>512</v>
       </c>
@@ -8499,11 +8499,11 @@
       </c>
     </row>
     <row r="139" spans="1:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A139" s="9" t="s">
+      <c r="A139" s="8" t="s">
         <v>514</v>
       </c>
-      <c r="B139" s="9"/>
-      <c r="C139" s="9"/>
+      <c r="B139" s="8"/>
+      <c r="C139" s="8"/>
       <c r="D139" s="4" t="s">
         <v>515</v>
       </c>
@@ -8533,11 +8533,11 @@
       </c>
     </row>
     <row r="140" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A140" s="9" t="s">
+      <c r="A140" s="8" t="s">
         <v>518</v>
       </c>
-      <c r="B140" s="9"/>
-      <c r="C140" s="9"/>
+      <c r="B140" s="8"/>
+      <c r="C140" s="8"/>
       <c r="D140" s="4" t="s">
         <v>519</v>
       </c>
@@ -8567,11 +8567,11 @@
       </c>
     </row>
     <row r="141" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A141" s="9" t="s">
+      <c r="A141" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="B141" s="9"/>
-      <c r="C141" s="9"/>
+      <c r="B141" s="8"/>
+      <c r="C141" s="8"/>
       <c r="D141" s="4" t="s">
         <v>523</v>
       </c>
@@ -8601,11 +8601,11 @@
       </c>
     </row>
     <row r="142" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A142" s="9" t="s">
+      <c r="A142" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="B142" s="9"/>
-      <c r="C142" s="9"/>
+      <c r="B142" s="8"/>
+      <c r="C142" s="8"/>
       <c r="D142" s="4" t="s">
         <v>526</v>
       </c>
@@ -8635,11 +8635,11 @@
       </c>
     </row>
     <row r="143" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A143" s="9" t="s">
+      <c r="A143" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="B143" s="9"/>
-      <c r="C143" s="9"/>
+      <c r="B143" s="8"/>
+      <c r="C143" s="8"/>
       <c r="D143" s="4" t="s">
         <v>529</v>
       </c>
@@ -8669,11 +8669,11 @@
       </c>
     </row>
     <row r="144" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A144" s="9" t="s">
+      <c r="A144" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="B144" s="9"/>
-      <c r="C144" s="9"/>
+      <c r="B144" s="8"/>
+      <c r="C144" s="8"/>
       <c r="D144" s="4" t="s">
         <v>532</v>
       </c>
@@ -8703,11 +8703,11 @@
       </c>
     </row>
     <row r="145" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A145" s="9" t="s">
+      <c r="A145" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="B145" s="9"/>
-      <c r="C145" s="9"/>
+      <c r="B145" s="8"/>
+      <c r="C145" s="8"/>
       <c r="D145" s="4" t="s">
         <v>535</v>
       </c>
@@ -8737,11 +8737,11 @@
       </c>
     </row>
     <row r="146" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A146" s="9" t="s">
+      <c r="A146" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="B146" s="9"/>
-      <c r="C146" s="9"/>
+      <c r="B146" s="8"/>
+      <c r="C146" s="8"/>
       <c r="D146" s="4" t="s">
         <v>538</v>
       </c>
@@ -8771,11 +8771,11 @@
       </c>
     </row>
     <row r="147" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A147" s="9" t="s">
+      <c r="A147" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="B147" s="9"/>
-      <c r="C147" s="9"/>
+      <c r="B147" s="8"/>
+      <c r="C147" s="8"/>
       <c r="D147" s="4" t="s">
         <v>541</v>
       </c>
@@ -8805,11 +8805,11 @@
       </c>
     </row>
     <row r="148" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A148" s="9" t="s">
+      <c r="A148" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="B148" s="9"/>
-      <c r="C148" s="9"/>
+      <c r="B148" s="8"/>
+      <c r="C148" s="8"/>
       <c r="D148" s="4" t="s">
         <v>544</v>
       </c>
@@ -8839,11 +8839,11 @@
       </c>
     </row>
     <row r="149" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A149" s="9" t="s">
+      <c r="A149" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="B149" s="9"/>
-      <c r="C149" s="9"/>
+      <c r="B149" s="8"/>
+      <c r="C149" s="8"/>
       <c r="D149" s="4" t="s">
         <v>547</v>
       </c>
@@ -8873,11 +8873,11 @@
       </c>
     </row>
     <row r="150" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A150" s="9" t="s">
+      <c r="A150" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="B150" s="9"/>
-      <c r="C150" s="9"/>
+      <c r="B150" s="8"/>
+      <c r="C150" s="8"/>
       <c r="D150" s="4" t="s">
         <v>550</v>
       </c>
@@ -8907,11 +8907,11 @@
       </c>
     </row>
     <row r="151" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A151" s="9" t="s">
+      <c r="A151" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="B151" s="9"/>
-      <c r="C151" s="9"/>
+      <c r="B151" s="8"/>
+      <c r="C151" s="8"/>
       <c r="D151" s="4" t="s">
         <v>553</v>
       </c>
@@ -8941,11 +8941,11 @@
       </c>
     </row>
     <row r="152" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A152" s="9" t="s">
+      <c r="A152" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="B152" s="9"/>
-      <c r="C152" s="9"/>
+      <c r="B152" s="8"/>
+      <c r="C152" s="8"/>
       <c r="D152" s="4" t="s">
         <v>556</v>
       </c>
@@ -8975,11 +8975,11 @@
       </c>
     </row>
     <row r="153" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A153" s="9" t="s">
+      <c r="A153" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="B153" s="9"/>
-      <c r="C153" s="9"/>
+      <c r="B153" s="8"/>
+      <c r="C153" s="8"/>
       <c r="D153" s="4" t="s">
         <v>559</v>
       </c>
@@ -9009,11 +9009,11 @@
       </c>
     </row>
     <row r="154" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A154" s="9" t="s">
+      <c r="A154" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="B154" s="9"/>
-      <c r="C154" s="9"/>
+      <c r="B154" s="8"/>
+      <c r="C154" s="8"/>
       <c r="D154" s="4" t="s">
         <v>562</v>
       </c>
@@ -9043,11 +9043,11 @@
       </c>
     </row>
     <row r="155" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A155" s="9" t="s">
+      <c r="A155" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="B155" s="9"/>
-      <c r="C155" s="9"/>
+      <c r="B155" s="8"/>
+      <c r="C155" s="8"/>
       <c r="D155" s="4" t="s">
         <v>565</v>
       </c>
@@ -9077,11 +9077,11 @@
       </c>
     </row>
     <row r="156" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A156" s="9" t="s">
+      <c r="A156" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="B156" s="9"/>
-      <c r="C156" s="9"/>
+      <c r="B156" s="8"/>
+      <c r="C156" s="8"/>
       <c r="D156" s="4" t="s">
         <v>568</v>
       </c>
@@ -9111,11 +9111,11 @@
       </c>
     </row>
     <row r="157" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A157" s="9" t="s">
+      <c r="A157" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="B157" s="9"/>
-      <c r="C157" s="9"/>
+      <c r="B157" s="8"/>
+      <c r="C157" s="8"/>
       <c r="D157" s="4" t="s">
         <v>570</v>
       </c>
@@ -9145,11 +9145,11 @@
       </c>
     </row>
     <row r="158" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A158" s="9" t="s">
+      <c r="A158" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="B158" s="9"/>
-      <c r="C158" s="9"/>
+      <c r="B158" s="8"/>
+      <c r="C158" s="8"/>
       <c r="D158" s="4" t="s">
         <v>573</v>
       </c>
@@ -9179,11 +9179,11 @@
       </c>
     </row>
     <row r="159" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A159" s="9" t="s">
+      <c r="A159" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="B159" s="9"/>
-      <c r="C159" s="9"/>
+      <c r="B159" s="8"/>
+      <c r="C159" s="8"/>
       <c r="D159" s="4" t="s">
         <v>576</v>
       </c>
@@ -9213,11 +9213,11 @@
       </c>
     </row>
     <row r="160" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A160" s="9" t="s">
+      <c r="A160" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="B160" s="9"/>
-      <c r="C160" s="9"/>
+      <c r="B160" s="8"/>
+      <c r="C160" s="8"/>
       <c r="D160" s="4" t="s">
         <v>578</v>
       </c>
@@ -9247,11 +9247,11 @@
       </c>
     </row>
     <row r="161" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A161" s="9" t="s">
+      <c r="A161" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="B161" s="9"/>
-      <c r="C161" s="9"/>
+      <c r="B161" s="8"/>
+      <c r="C161" s="8"/>
       <c r="D161" s="4" t="s">
         <v>581</v>
       </c>
@@ -9281,11 +9281,11 @@
       </c>
     </row>
     <row r="162" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A162" s="9" t="s">
+      <c r="A162" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="B162" s="9"/>
-      <c r="C162" s="9"/>
+      <c r="B162" s="8"/>
+      <c r="C162" s="8"/>
       <c r="D162" s="4" t="s">
         <v>584</v>
       </c>
@@ -9315,11 +9315,11 @@
       </c>
     </row>
     <row r="163" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A163" s="9" t="s">
+      <c r="A163" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="B163" s="9"/>
-      <c r="C163" s="9"/>
+      <c r="B163" s="8"/>
+      <c r="C163" s="8"/>
       <c r="D163" s="4" t="s">
         <v>588</v>
       </c>
@@ -9349,11 +9349,11 @@
       </c>
     </row>
     <row r="164" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A164" s="9" t="s">
+      <c r="A164" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="B164" s="9"/>
-      <c r="C164" s="9"/>
+      <c r="B164" s="8"/>
+      <c r="C164" s="8"/>
       <c r="D164" s="4" t="s">
         <v>591</v>
       </c>
@@ -9383,11 +9383,11 @@
       </c>
     </row>
     <row r="165" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A165" s="9" t="s">
+      <c r="A165" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="B165" s="9"/>
-      <c r="C165" s="9"/>
+      <c r="B165" s="8"/>
+      <c r="C165" s="8"/>
       <c r="D165" s="4" t="s">
         <v>594</v>
       </c>
@@ -9417,11 +9417,11 @@
       </c>
     </row>
     <row r="166" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A166" s="9" t="s">
+      <c r="A166" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="B166" s="9"/>
-      <c r="C166" s="9"/>
+      <c r="B166" s="8"/>
+      <c r="C166" s="8"/>
       <c r="D166" s="4" t="s">
         <v>597</v>
       </c>
@@ -9451,11 +9451,11 @@
       </c>
     </row>
     <row r="167" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A167" s="9" t="s">
+      <c r="A167" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="B167" s="9"/>
-      <c r="C167" s="9"/>
+      <c r="B167" s="8"/>
+      <c r="C167" s="8"/>
       <c r="D167" s="4" t="s">
         <v>600</v>
       </c>
@@ -9485,11 +9485,11 @@
       </c>
     </row>
     <row r="168" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A168" s="9" t="s">
+      <c r="A168" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="B168" s="9"/>
-      <c r="C168" s="9"/>
+      <c r="B168" s="8"/>
+      <c r="C168" s="8"/>
       <c r="D168" s="4" t="s">
         <v>603</v>
       </c>
@@ -9519,11 +9519,11 @@
       </c>
     </row>
     <row r="169" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A169" s="9" t="s">
+      <c r="A169" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="B169" s="9"/>
-      <c r="C169" s="9"/>
+      <c r="B169" s="8"/>
+      <c r="C169" s="8"/>
       <c r="D169" s="4" t="s">
         <v>606</v>
       </c>
@@ -9553,11 +9553,11 @@
       </c>
     </row>
     <row r="170" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A170" s="9" t="s">
+      <c r="A170" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="B170" s="9"/>
-      <c r="C170" s="9"/>
+      <c r="B170" s="8"/>
+      <c r="C170" s="8"/>
       <c r="D170" s="4" t="s">
         <v>608</v>
       </c>
@@ -9587,11 +9587,11 @@
       </c>
     </row>
     <row r="171" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A171" s="9" t="s">
+      <c r="A171" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="B171" s="9"/>
-      <c r="C171" s="9"/>
+      <c r="B171" s="8"/>
+      <c r="C171" s="8"/>
       <c r="D171" s="4" t="s">
         <v>612</v>
       </c>
@@ -9621,11 +9621,11 @@
       </c>
     </row>
     <row r="172" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A172" s="9" t="s">
+      <c r="A172" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="B172" s="9"/>
-      <c r="C172" s="9"/>
+      <c r="B172" s="8"/>
+      <c r="C172" s="8"/>
       <c r="D172" s="4" t="s">
         <v>613</v>
       </c>
@@ -9655,11 +9655,11 @@
       </c>
     </row>
     <row r="173" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A173" s="9" t="s">
+      <c r="A173" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="B173" s="9"/>
-      <c r="C173" s="9"/>
+      <c r="B173" s="8"/>
+      <c r="C173" s="8"/>
       <c r="D173" s="4" t="s">
         <v>616</v>
       </c>
@@ -9689,11 +9689,11 @@
       </c>
     </row>
     <row r="174" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A174" s="9" t="s">
+      <c r="A174" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="B174" s="9"/>
-      <c r="C174" s="9"/>
+      <c r="B174" s="8"/>
+      <c r="C174" s="8"/>
       <c r="D174" s="4" t="s">
         <v>619</v>
       </c>
@@ -9723,11 +9723,11 @@
       </c>
     </row>
     <row r="175" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A175" s="9" t="s">
+      <c r="A175" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="B175" s="9"/>
-      <c r="C175" s="9"/>
+      <c r="B175" s="8"/>
+      <c r="C175" s="8"/>
       <c r="D175" s="4" t="s">
         <v>622</v>
       </c>
@@ -9757,11 +9757,11 @@
       </c>
     </row>
     <row r="176" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A176" s="9" t="s">
+      <c r="A176" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="B176" s="9"/>
-      <c r="C176" s="9"/>
+      <c r="B176" s="8"/>
+      <c r="C176" s="8"/>
       <c r="D176" s="4" t="s">
         <v>626</v>
       </c>
@@ -9791,11 +9791,11 @@
       </c>
     </row>
     <row r="177" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A177" s="9" t="s">
+      <c r="A177" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="B177" s="9"/>
-      <c r="C177" s="9"/>
+      <c r="B177" s="8"/>
+      <c r="C177" s="8"/>
       <c r="D177" s="4" t="s">
         <v>628</v>
       </c>
@@ -9825,11 +9825,11 @@
       </c>
     </row>
     <row r="178" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A178" s="9" t="s">
+      <c r="A178" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="B178" s="9"/>
-      <c r="C178" s="9"/>
+      <c r="B178" s="8"/>
+      <c r="C178" s="8"/>
       <c r="D178" s="4" t="s">
         <v>631</v>
       </c>
@@ -9859,11 +9859,11 @@
       </c>
     </row>
     <row r="179" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A179" s="9" t="s">
+      <c r="A179" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="B179" s="9"/>
-      <c r="C179" s="9"/>
+      <c r="B179" s="8"/>
+      <c r="C179" s="8"/>
       <c r="D179" s="4" t="s">
         <v>634</v>
       </c>
@@ -9893,11 +9893,11 @@
       </c>
     </row>
     <row r="180" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A180" s="9" t="s">
+      <c r="A180" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="B180" s="9"/>
-      <c r="C180" s="9"/>
+      <c r="B180" s="8"/>
+      <c r="C180" s="8"/>
       <c r="D180" s="4" t="s">
         <v>636</v>
       </c>
@@ -9927,11 +9927,11 @@
       </c>
     </row>
     <row r="181" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A181" s="9" t="s">
+      <c r="A181" s="8" t="s">
         <v>639</v>
       </c>
-      <c r="B181" s="9"/>
-      <c r="C181" s="9"/>
+      <c r="B181" s="8"/>
+      <c r="C181" s="8"/>
       <c r="D181" s="4" t="s">
         <v>640</v>
       </c>
@@ -9961,11 +9961,11 @@
       </c>
     </row>
     <row r="182" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A182" s="9" t="s">
+      <c r="A182" s="8" t="s">
         <v>642</v>
       </c>
-      <c r="B182" s="9"/>
-      <c r="C182" s="9"/>
+      <c r="B182" s="8"/>
+      <c r="C182" s="8"/>
       <c r="D182" s="4" t="s">
         <v>642</v>
       </c>
@@ -9995,11 +9995,11 @@
       </c>
     </row>
     <row r="183" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A183" s="9" t="s">
+      <c r="A183" s="8" t="s">
         <v>645</v>
       </c>
-      <c r="B183" s="9"/>
-      <c r="C183" s="9"/>
+      <c r="B183" s="8"/>
+      <c r="C183" s="8"/>
       <c r="D183" s="4" t="s">
         <v>646</v>
       </c>
@@ -10029,11 +10029,11 @@
       </c>
     </row>
     <row r="184" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A184" s="9" t="s">
+      <c r="A184" s="8" t="s">
         <v>649</v>
       </c>
-      <c r="B184" s="9"/>
-      <c r="C184" s="9"/>
+      <c r="B184" s="8"/>
+      <c r="C184" s="8"/>
       <c r="D184" s="4" t="s">
         <v>650</v>
       </c>
@@ -10063,11 +10063,11 @@
       </c>
     </row>
     <row r="185" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A185" s="9" t="s">
+      <c r="A185" s="8" t="s">
         <v>653</v>
       </c>
-      <c r="B185" s="9"/>
-      <c r="C185" s="9"/>
+      <c r="B185" s="8"/>
+      <c r="C185" s="8"/>
       <c r="D185" s="4" t="s">
         <v>654</v>
       </c>
@@ -10097,11 +10097,11 @@
       </c>
     </row>
     <row r="186" spans="1:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A186" s="9" t="s">
+      <c r="A186" s="8" t="s">
         <v>658</v>
       </c>
-      <c r="B186" s="9"/>
-      <c r="C186" s="9"/>
+      <c r="B186" s="8"/>
+      <c r="C186" s="8"/>
       <c r="D186" s="4" t="s">
         <v>659</v>
       </c>
@@ -10131,11 +10131,11 @@
       </c>
     </row>
     <row r="187" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A187" s="9" t="s">
+      <c r="A187" s="8" t="s">
         <v>661</v>
       </c>
-      <c r="B187" s="9"/>
-      <c r="C187" s="9"/>
+      <c r="B187" s="8"/>
+      <c r="C187" s="8"/>
       <c r="D187" s="4" t="s">
         <v>661</v>
       </c>
@@ -10165,11 +10165,11 @@
       </c>
     </row>
     <row r="188" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A188" s="9" t="s">
+      <c r="A188" s="8" t="s">
         <v>664</v>
       </c>
-      <c r="B188" s="9"/>
-      <c r="C188" s="9"/>
+      <c r="B188" s="8"/>
+      <c r="C188" s="8"/>
       <c r="D188" s="4" t="s">
         <v>665</v>
       </c>
@@ -10199,11 +10199,11 @@
       </c>
     </row>
     <row r="189" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A189" s="9" t="s">
+      <c r="A189" s="8" t="s">
         <v>669</v>
       </c>
-      <c r="B189" s="9"/>
-      <c r="C189" s="9"/>
+      <c r="B189" s="8"/>
+      <c r="C189" s="8"/>
       <c r="D189" s="4" t="s">
         <v>670</v>
       </c>
@@ -10233,11 +10233,11 @@
       </c>
     </row>
     <row r="190" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A190" s="9" t="s">
+      <c r="A190" s="8" t="s">
         <v>673</v>
       </c>
-      <c r="B190" s="9"/>
-      <c r="C190" s="9"/>
+      <c r="B190" s="8"/>
+      <c r="C190" s="8"/>
       <c r="D190" s="4" t="s">
         <v>674</v>
       </c>
@@ -10267,11 +10267,11 @@
       </c>
     </row>
     <row r="191" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A191" s="9" t="s">
+      <c r="A191" s="8" t="s">
         <v>653</v>
       </c>
-      <c r="B191" s="9"/>
-      <c r="C191" s="9"/>
+      <c r="B191" s="8"/>
+      <c r="C191" s="8"/>
       <c r="D191" s="4" t="s">
         <v>678</v>
       </c>
@@ -10301,11 +10301,11 @@
       </c>
     </row>
     <row r="192" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A192" s="9" t="s">
+      <c r="A192" s="8" t="s">
         <v>681</v>
       </c>
-      <c r="B192" s="9"/>
-      <c r="C192" s="9"/>
+      <c r="B192" s="8"/>
+      <c r="C192" s="8"/>
       <c r="D192" s="4" t="s">
         <v>682</v>
       </c>
@@ -10335,11 +10335,11 @@
       </c>
     </row>
     <row r="193" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A193" s="9" t="s">
+      <c r="A193" s="8" t="s">
         <v>685</v>
       </c>
-      <c r="B193" s="9"/>
-      <c r="C193" s="9"/>
+      <c r="B193" s="8"/>
+      <c r="C193" s="8"/>
       <c r="D193" s="4" t="s">
         <v>685</v>
       </c>
@@ -10369,11 +10369,11 @@
       </c>
     </row>
     <row r="194" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A194" s="9" t="s">
+      <c r="A194" s="8" t="s">
         <v>688</v>
       </c>
-      <c r="B194" s="9"/>
-      <c r="C194" s="9"/>
+      <c r="B194" s="8"/>
+      <c r="C194" s="8"/>
       <c r="D194" s="4" t="s">
         <v>688</v>
       </c>
@@ -10403,11 +10403,11 @@
       </c>
     </row>
     <row r="195" spans="1:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A195" s="9" t="s">
+      <c r="A195" s="8" t="s">
         <v>691</v>
       </c>
-      <c r="B195" s="9"/>
-      <c r="C195" s="9"/>
+      <c r="B195" s="8"/>
+      <c r="C195" s="8"/>
       <c r="D195" s="4" t="s">
         <v>692</v>
       </c>
@@ -10437,11 +10437,11 @@
       </c>
     </row>
     <row r="196" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A196" s="9" t="s">
+      <c r="A196" s="8" t="s">
         <v>695</v>
       </c>
-      <c r="B196" s="9"/>
-      <c r="C196" s="9"/>
+      <c r="B196" s="8"/>
+      <c r="C196" s="8"/>
       <c r="D196" s="4" t="s">
         <v>696</v>
       </c>
@@ -10471,11 +10471,11 @@
       </c>
     </row>
     <row r="197" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A197" s="9" t="s">
+      <c r="A197" s="8" t="s">
         <v>699</v>
       </c>
-      <c r="B197" s="9"/>
-      <c r="C197" s="9"/>
+      <c r="B197" s="8"/>
+      <c r="C197" s="8"/>
       <c r="D197" s="4" t="s">
         <v>700</v>
       </c>
@@ -10505,11 +10505,11 @@
       </c>
     </row>
     <row r="198" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A198" s="9" t="s">
+      <c r="A198" s="8" t="s">
         <v>703</v>
       </c>
-      <c r="B198" s="9"/>
-      <c r="C198" s="9"/>
+      <c r="B198" s="8"/>
+      <c r="C198" s="8"/>
       <c r="D198" s="4" t="s">
         <v>704</v>
       </c>
@@ -10539,11 +10539,11 @@
       </c>
     </row>
     <row r="199" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A199" s="9" t="s">
+      <c r="A199" s="8" t="s">
         <v>707</v>
       </c>
-      <c r="B199" s="9"/>
-      <c r="C199" s="9"/>
+      <c r="B199" s="8"/>
+      <c r="C199" s="8"/>
       <c r="D199" s="4" t="s">
         <v>707</v>
       </c>
@@ -10573,11 +10573,11 @@
       </c>
     </row>
     <row r="200" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A200" s="9" t="s">
+      <c r="A200" s="8" t="s">
         <v>709</v>
       </c>
-      <c r="B200" s="9"/>
-      <c r="C200" s="9"/>
+      <c r="B200" s="8"/>
+      <c r="C200" s="8"/>
       <c r="D200" s="4" t="s">
         <v>709</v>
       </c>
@@ -10607,11 +10607,11 @@
       </c>
     </row>
     <row r="201" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A201" s="9" t="s">
+      <c r="A201" s="8" t="s">
         <v>712</v>
       </c>
-      <c r="B201" s="9"/>
-      <c r="C201" s="9"/>
+      <c r="B201" s="8"/>
+      <c r="C201" s="8"/>
       <c r="D201" s="4" t="s">
         <v>713</v>
       </c>
@@ -10641,11 +10641,11 @@
       </c>
     </row>
     <row r="202" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A202" s="9" t="s">
+      <c r="A202" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B202" s="9"/>
-      <c r="C202" s="9"/>
+      <c r="B202" s="8"/>
+      <c r="C202" s="8"/>
       <c r="D202" s="4" t="s">
         <v>716</v>
       </c>
@@ -10675,11 +10675,11 @@
       </c>
     </row>
     <row r="203" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A203" s="9" t="s">
+      <c r="A203" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="B203" s="9"/>
-      <c r="C203" s="9"/>
+      <c r="B203" s="8"/>
+      <c r="C203" s="8"/>
       <c r="D203" s="4" t="s">
         <v>720</v>
       </c>
@@ -10709,11 +10709,11 @@
       </c>
     </row>
     <row r="204" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A204" s="9" t="s">
+      <c r="A204" s="8" t="s">
         <v>722</v>
       </c>
-      <c r="B204" s="9"/>
-      <c r="C204" s="9"/>
+      <c r="B204" s="8"/>
+      <c r="C204" s="8"/>
       <c r="D204" s="4" t="s">
         <v>723</v>
       </c>
@@ -10743,11 +10743,11 @@
       </c>
     </row>
     <row r="205" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A205" s="9" t="s">
+      <c r="A205" s="8" t="s">
         <v>726</v>
       </c>
-      <c r="B205" s="9"/>
-      <c r="C205" s="9"/>
+      <c r="B205" s="8"/>
+      <c r="C205" s="8"/>
       <c r="D205" s="4" t="s">
         <v>726</v>
       </c>
@@ -10777,11 +10777,11 @@
       </c>
     </row>
     <row r="206" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A206" s="9" t="s">
+      <c r="A206" s="8" t="s">
         <v>729</v>
       </c>
-      <c r="B206" s="9"/>
-      <c r="C206" s="9"/>
+      <c r="B206" s="8"/>
+      <c r="C206" s="8"/>
       <c r="D206" s="4" t="s">
         <v>730</v>
       </c>
@@ -10811,11 +10811,11 @@
       </c>
     </row>
     <row r="207" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A207" s="9" t="s">
+      <c r="A207" s="8" t="s">
         <v>733</v>
       </c>
-      <c r="B207" s="9"/>
-      <c r="C207" s="9"/>
+      <c r="B207" s="8"/>
+      <c r="C207" s="8"/>
       <c r="D207" s="4" t="s">
         <v>734</v>
       </c>
@@ -10845,11 +10845,11 @@
       </c>
     </row>
     <row r="208" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A208" s="9" t="s">
+      <c r="A208" s="8" t="s">
         <v>737</v>
       </c>
-      <c r="B208" s="9"/>
-      <c r="C208" s="9"/>
+      <c r="B208" s="8"/>
+      <c r="C208" s="8"/>
       <c r="D208" s="4" t="s">
         <v>738</v>
       </c>
@@ -10879,11 +10879,11 @@
       </c>
     </row>
     <row r="209" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A209" s="9" t="s">
+      <c r="A209" s="8" t="s">
         <v>737</v>
       </c>
-      <c r="B209" s="9"/>
-      <c r="C209" s="9"/>
+      <c r="B209" s="8"/>
+      <c r="C209" s="8"/>
       <c r="D209" s="4" t="s">
         <v>741</v>
       </c>
@@ -10913,11 +10913,11 @@
       </c>
     </row>
     <row r="210" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A210" s="9" t="s">
+      <c r="A210" s="8" t="s">
         <v>737</v>
       </c>
-      <c r="B210" s="9"/>
-      <c r="C210" s="9"/>
+      <c r="B210" s="8"/>
+      <c r="C210" s="8"/>
       <c r="D210" s="4" t="s">
         <v>744</v>
       </c>
@@ -10947,11 +10947,11 @@
       </c>
     </row>
     <row r="211" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A211" s="9" t="s">
+      <c r="A211" s="8" t="s">
         <v>737</v>
       </c>
-      <c r="B211" s="9"/>
-      <c r="C211" s="9"/>
+      <c r="B211" s="8"/>
+      <c r="C211" s="8"/>
       <c r="D211" s="4" t="s">
         <v>747</v>
       </c>
@@ -10981,11 +10981,11 @@
       </c>
     </row>
     <row r="212" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A212" s="9" t="s">
+      <c r="A212" s="8" t="s">
         <v>737</v>
       </c>
-      <c r="B212" s="9"/>
-      <c r="C212" s="9"/>
+      <c r="B212" s="8"/>
+      <c r="C212" s="8"/>
       <c r="D212" s="4" t="s">
         <v>750</v>
       </c>
@@ -11015,11 +11015,11 @@
       </c>
     </row>
     <row r="213" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A213" s="9" t="s">
+      <c r="A213" s="8" t="s">
         <v>737</v>
       </c>
-      <c r="B213" s="9"/>
-      <c r="C213" s="9"/>
+      <c r="B213" s="8"/>
+      <c r="C213" s="8"/>
       <c r="D213" s="4" t="s">
         <v>753</v>
       </c>
@@ -11049,11 +11049,11 @@
       </c>
     </row>
     <row r="214" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A214" s="9" t="s">
+      <c r="A214" s="8" t="s">
         <v>737</v>
       </c>
-      <c r="B214" s="9"/>
-      <c r="C214" s="9"/>
+      <c r="B214" s="8"/>
+      <c r="C214" s="8"/>
       <c r="D214" s="4" t="s">
         <v>756</v>
       </c>
@@ -11083,11 +11083,11 @@
       </c>
     </row>
     <row r="215" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A215" s="9" t="s">
+      <c r="A215" s="8" t="s">
         <v>737</v>
       </c>
-      <c r="B215" s="9"/>
-      <c r="C215" s="9"/>
+      <c r="B215" s="8"/>
+      <c r="C215" s="8"/>
       <c r="D215" s="4" t="s">
         <v>758</v>
       </c>
@@ -11117,11 +11117,11 @@
       </c>
     </row>
     <row r="216" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A216" s="9" t="s">
+      <c r="A216" s="8" t="s">
         <v>737</v>
       </c>
-      <c r="B216" s="9"/>
-      <c r="C216" s="9"/>
+      <c r="B216" s="8"/>
+      <c r="C216" s="8"/>
       <c r="D216" s="4" t="s">
         <v>758</v>
       </c>
@@ -11151,11 +11151,11 @@
       </c>
     </row>
     <row r="217" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A217" s="9" t="s">
+      <c r="A217" s="8" t="s">
         <v>737</v>
       </c>
-      <c r="B217" s="9"/>
-      <c r="C217" s="9"/>
+      <c r="B217" s="8"/>
+      <c r="C217" s="8"/>
       <c r="D217" s="4" t="s">
         <v>762</v>
       </c>
@@ -11185,11 +11185,11 @@
       </c>
     </row>
     <row r="218" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A218" s="9" t="s">
+      <c r="A218" s="8" t="s">
         <v>737</v>
       </c>
-      <c r="B218" s="9"/>
-      <c r="C218" s="9"/>
+      <c r="B218" s="8"/>
+      <c r="C218" s="8"/>
       <c r="D218" s="4" t="s">
         <v>765</v>
       </c>
@@ -11219,11 +11219,11 @@
       </c>
     </row>
     <row r="219" spans="1:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A219" s="9" t="s">
+      <c r="A219" s="8" t="s">
         <v>767</v>
       </c>
-      <c r="B219" s="9"/>
-      <c r="C219" s="9"/>
+      <c r="B219" s="8"/>
+      <c r="C219" s="8"/>
       <c r="D219" s="4" t="s">
         <v>768</v>
       </c>
@@ -11253,11 +11253,11 @@
       </c>
     </row>
     <row r="220" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A220" s="9" t="s">
+      <c r="A220" s="8" t="s">
         <v>771</v>
       </c>
-      <c r="B220" s="9"/>
-      <c r="C220" s="9"/>
+      <c r="B220" s="8"/>
+      <c r="C220" s="8"/>
       <c r="D220" s="4" t="s">
         <v>772</v>
       </c>
@@ -11287,11 +11287,11 @@
       </c>
     </row>
     <row r="221" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A221" s="9" t="s">
+      <c r="A221" s="8" t="s">
         <v>775</v>
       </c>
-      <c r="B221" s="9"/>
-      <c r="C221" s="9"/>
+      <c r="B221" s="8"/>
+      <c r="C221" s="8"/>
       <c r="D221" s="4" t="s">
         <v>776</v>
       </c>
@@ -11321,11 +11321,11 @@
       </c>
     </row>
     <row r="222" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A222" s="9" t="s">
+      <c r="A222" s="8" t="s">
         <v>779</v>
       </c>
-      <c r="B222" s="9"/>
-      <c r="C222" s="9"/>
+      <c r="B222" s="8"/>
+      <c r="C222" s="8"/>
       <c r="D222" s="4" t="s">
         <v>780</v>
       </c>
@@ -11355,11 +11355,11 @@
       </c>
     </row>
     <row r="223" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A223" s="9" t="s">
+      <c r="A223" s="8" t="s">
         <v>783</v>
       </c>
-      <c r="B223" s="9"/>
-      <c r="C223" s="9"/>
+      <c r="B223" s="8"/>
+      <c r="C223" s="8"/>
       <c r="D223" s="4" t="s">
         <v>784</v>
       </c>
@@ -11389,11 +11389,11 @@
       </c>
     </row>
     <row r="224" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A224" s="9" t="s">
+      <c r="A224" s="8" t="s">
         <v>783</v>
       </c>
-      <c r="B224" s="9"/>
-      <c r="C224" s="9"/>
+      <c r="B224" s="8"/>
+      <c r="C224" s="8"/>
       <c r="D224" s="4" t="s">
         <v>784</v>
       </c>
@@ -11423,11 +11423,11 @@
       </c>
     </row>
     <row r="225" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A225" s="9" t="s">
+      <c r="A225" s="8" t="s">
         <v>783</v>
       </c>
-      <c r="B225" s="9"/>
-      <c r="C225" s="9"/>
+      <c r="B225" s="8"/>
+      <c r="C225" s="8"/>
       <c r="D225" s="4" t="s">
         <v>788</v>
       </c>
@@ -11457,11 +11457,11 @@
       </c>
     </row>
     <row r="226" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A226" s="9" t="s">
+      <c r="A226" s="8" t="s">
         <v>783</v>
       </c>
-      <c r="B226" s="9"/>
-      <c r="C226" s="9"/>
+      <c r="B226" s="8"/>
+      <c r="C226" s="8"/>
       <c r="D226" s="4" t="s">
         <v>788</v>
       </c>
@@ -11491,11 +11491,11 @@
       </c>
     </row>
     <row r="227" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A227" s="9" t="s">
+      <c r="A227" s="8" t="s">
         <v>793</v>
       </c>
-      <c r="B227" s="9"/>
-      <c r="C227" s="9"/>
+      <c r="B227" s="8"/>
+      <c r="C227" s="8"/>
       <c r="D227" s="4" t="s">
         <v>794</v>
       </c>
@@ -11525,11 +11525,11 @@
       </c>
     </row>
     <row r="228" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A228" s="9" t="s">
+      <c r="A228" s="8" t="s">
         <v>797</v>
       </c>
-      <c r="B228" s="9"/>
-      <c r="C228" s="9"/>
+      <c r="B228" s="8"/>
+      <c r="C228" s="8"/>
       <c r="D228" s="4" t="s">
         <v>798</v>
       </c>
@@ -11559,11 +11559,11 @@
       </c>
     </row>
     <row r="229" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A229" s="9" t="s">
+      <c r="A229" s="8" t="s">
         <v>802</v>
       </c>
-      <c r="B229" s="9"/>
-      <c r="C229" s="9"/>
+      <c r="B229" s="8"/>
+      <c r="C229" s="8"/>
       <c r="D229" s="4" t="s">
         <v>803</v>
       </c>
@@ -11593,11 +11593,11 @@
       </c>
     </row>
     <row r="230" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A230" s="9" t="s">
+      <c r="A230" s="8" t="s">
         <v>807</v>
       </c>
-      <c r="B230" s="9"/>
-      <c r="C230" s="9"/>
+      <c r="B230" s="8"/>
+      <c r="C230" s="8"/>
       <c r="D230" s="4" t="s">
         <v>808</v>
       </c>
@@ -11627,11 +11627,11 @@
       </c>
     </row>
     <row r="231" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A231" s="9" t="s">
+      <c r="A231" s="8" t="s">
         <v>807</v>
       </c>
-      <c r="B231" s="9"/>
-      <c r="C231" s="9"/>
+      <c r="B231" s="8"/>
+      <c r="C231" s="8"/>
       <c r="D231" s="4" t="s">
         <v>811</v>
       </c>
@@ -11661,11 +11661,11 @@
       </c>
     </row>
     <row r="232" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A232" s="9" t="s">
+      <c r="A232" s="8" t="s">
         <v>807</v>
       </c>
-      <c r="B232" s="9"/>
-      <c r="C232" s="9"/>
+      <c r="B232" s="8"/>
+      <c r="C232" s="8"/>
       <c r="D232" s="4" t="s">
         <v>814</v>
       </c>
@@ -11695,11 +11695,11 @@
       </c>
     </row>
     <row r="233" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A233" s="9" t="s">
+      <c r="A233" s="8" t="s">
         <v>817</v>
       </c>
-      <c r="B233" s="9"/>
-      <c r="C233" s="9"/>
+      <c r="B233" s="8"/>
+      <c r="C233" s="8"/>
       <c r="D233" s="4" t="s">
         <v>818</v>
       </c>
@@ -11729,11 +11729,11 @@
       </c>
     </row>
     <row r="234" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A234" s="9" t="s">
+      <c r="A234" s="8" t="s">
         <v>821</v>
       </c>
-      <c r="B234" s="9"/>
-      <c r="C234" s="9"/>
+      <c r="B234" s="8"/>
+      <c r="C234" s="8"/>
       <c r="D234" s="4" t="s">
         <v>821</v>
       </c>
@@ -11763,11 +11763,11 @@
       </c>
     </row>
     <row r="235" spans="1:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A235" s="9" t="s">
+      <c r="A235" s="8" t="s">
         <v>824</v>
       </c>
-      <c r="B235" s="9"/>
-      <c r="C235" s="9"/>
+      <c r="B235" s="8"/>
+      <c r="C235" s="8"/>
       <c r="D235" s="4" t="s">
         <v>825</v>
       </c>
@@ -11797,11 +11797,11 @@
       </c>
     </row>
     <row r="236" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A236" s="9" t="s">
+      <c r="A236" s="8" t="s">
         <v>828</v>
       </c>
-      <c r="B236" s="9"/>
-      <c r="C236" s="9"/>
+      <c r="B236" s="8"/>
+      <c r="C236" s="8"/>
       <c r="D236" s="4" t="s">
         <v>829</v>
       </c>
@@ -11831,11 +11831,11 @@
       </c>
     </row>
     <row r="237" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A237" s="9" t="s">
+      <c r="A237" s="8" t="s">
         <v>832</v>
       </c>
-      <c r="B237" s="9"/>
-      <c r="C237" s="9"/>
+      <c r="B237" s="8"/>
+      <c r="C237" s="8"/>
       <c r="D237" s="4" t="s">
         <v>833</v>
       </c>
@@ -11865,11 +11865,11 @@
       </c>
     </row>
     <row r="238" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A238" s="9" t="s">
+      <c r="A238" s="8" t="s">
         <v>836</v>
       </c>
-      <c r="B238" s="9"/>
-      <c r="C238" s="9"/>
+      <c r="B238" s="8"/>
+      <c r="C238" s="8"/>
       <c r="D238" s="4" t="s">
         <v>836</v>
       </c>
@@ -11899,11 +11899,11 @@
       </c>
     </row>
     <row r="239" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A239" s="9" t="s">
+      <c r="A239" s="8" t="s">
         <v>839</v>
       </c>
-      <c r="B239" s="9"/>
-      <c r="C239" s="9"/>
+      <c r="B239" s="8"/>
+      <c r="C239" s="8"/>
       <c r="D239" s="4" t="s">
         <v>840</v>
       </c>
@@ -11933,11 +11933,11 @@
       </c>
     </row>
     <row r="240" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A240" s="9" t="s">
+      <c r="A240" s="8" t="s">
         <v>842</v>
       </c>
-      <c r="B240" s="9"/>
-      <c r="C240" s="9"/>
+      <c r="B240" s="8"/>
+      <c r="C240" s="8"/>
       <c r="D240" s="4" t="s">
         <v>842</v>
       </c>
@@ -11967,11 +11967,11 @@
       </c>
     </row>
     <row r="241" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A241" s="9" t="s">
+      <c r="A241" s="8" t="s">
         <v>845</v>
       </c>
-      <c r="B241" s="9"/>
-      <c r="C241" s="9"/>
+      <c r="B241" s="8"/>
+      <c r="C241" s="8"/>
       <c r="D241" s="4" t="s">
         <v>845</v>
       </c>
@@ -12001,11 +12001,11 @@
       </c>
     </row>
     <row r="242" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A242" s="9" t="s">
+      <c r="A242" s="8" t="s">
         <v>848</v>
       </c>
-      <c r="B242" s="9"/>
-      <c r="C242" s="9"/>
+      <c r="B242" s="8"/>
+      <c r="C242" s="8"/>
       <c r="D242" s="4" t="s">
         <v>849</v>
       </c>
@@ -12035,11 +12035,11 @@
       </c>
     </row>
     <row r="243" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A243" s="9" t="s">
+      <c r="A243" s="8" t="s">
         <v>852</v>
       </c>
-      <c r="B243" s="9"/>
-      <c r="C243" s="9"/>
+      <c r="B243" s="8"/>
+      <c r="C243" s="8"/>
       <c r="D243" s="4" t="s">
         <v>852</v>
       </c>
@@ -12069,11 +12069,11 @@
       </c>
     </row>
     <row r="244" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A244" s="9" t="s">
+      <c r="A244" s="8" t="s">
         <v>855</v>
       </c>
-      <c r="B244" s="9"/>
-      <c r="C244" s="9"/>
+      <c r="B244" s="8"/>
+      <c r="C244" s="8"/>
       <c r="D244" s="4" t="s">
         <v>856</v>
       </c>
@@ -12103,11 +12103,11 @@
       </c>
     </row>
     <row r="245" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A245" s="9" t="s">
+      <c r="A245" s="8" t="s">
         <v>859</v>
       </c>
-      <c r="B245" s="9"/>
-      <c r="C245" s="9"/>
+      <c r="B245" s="8"/>
+      <c r="C245" s="8"/>
       <c r="D245" s="4" t="s">
         <v>860</v>
       </c>
@@ -12137,11 +12137,11 @@
       </c>
     </row>
     <row r="246" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A246" s="9" t="s">
+      <c r="A246" s="8" t="s">
         <v>863</v>
       </c>
-      <c r="B246" s="9"/>
-      <c r="C246" s="9"/>
+      <c r="B246" s="8"/>
+      <c r="C246" s="8"/>
       <c r="D246" s="4" t="s">
         <v>863</v>
       </c>
@@ -12171,11 +12171,11 @@
       </c>
     </row>
     <row r="247" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A247" s="9" t="s">
+      <c r="A247" s="8" t="s">
         <v>866</v>
       </c>
-      <c r="B247" s="9"/>
-      <c r="C247" s="9"/>
+      <c r="B247" s="8"/>
+      <c r="C247" s="8"/>
       <c r="D247" s="4" t="s">
         <v>866</v>
       </c>
@@ -12205,11 +12205,11 @@
       </c>
     </row>
     <row r="248" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A248" s="9" t="s">
+      <c r="A248" s="8" t="s">
         <v>869</v>
       </c>
-      <c r="B248" s="9"/>
-      <c r="C248" s="9"/>
+      <c r="B248" s="8"/>
+      <c r="C248" s="8"/>
       <c r="D248" s="4" t="s">
         <v>870</v>
       </c>
@@ -12239,11 +12239,11 @@
       </c>
     </row>
     <row r="249" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A249" s="9" t="s">
+      <c r="A249" s="8" t="s">
         <v>873</v>
       </c>
-      <c r="B249" s="9"/>
-      <c r="C249" s="9"/>
+      <c r="B249" s="8"/>
+      <c r="C249" s="8"/>
       <c r="D249" s="4" t="s">
         <v>874</v>
       </c>
@@ -12273,11 +12273,11 @@
       </c>
     </row>
     <row r="250" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A250" s="9" t="s">
+      <c r="A250" s="8" t="s">
         <v>877</v>
       </c>
-      <c r="B250" s="9"/>
-      <c r="C250" s="9"/>
+      <c r="B250" s="8"/>
+      <c r="C250" s="8"/>
       <c r="D250" s="4" t="s">
         <v>878</v>
       </c>
@@ -12307,11 +12307,11 @@
       </c>
     </row>
     <row r="251" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A251" s="9" t="s">
+      <c r="A251" s="8" t="s">
         <v>881</v>
       </c>
-      <c r="B251" s="9"/>
-      <c r="C251" s="9"/>
+      <c r="B251" s="8"/>
+      <c r="C251" s="8"/>
       <c r="D251" s="4" t="s">
         <v>882</v>
       </c>
@@ -12341,11 +12341,11 @@
       </c>
     </row>
     <row r="252" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A252" s="9" t="s">
+      <c r="A252" s="8" t="s">
         <v>885</v>
       </c>
-      <c r="B252" s="9"/>
-      <c r="C252" s="9"/>
+      <c r="B252" s="8"/>
+      <c r="C252" s="8"/>
       <c r="D252" s="4" t="s">
         <v>886</v>
       </c>
@@ -12375,11 +12375,11 @@
       </c>
     </row>
     <row r="253" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A253" s="9" t="s">
+      <c r="A253" s="8" t="s">
         <v>889</v>
       </c>
-      <c r="B253" s="9"/>
-      <c r="C253" s="9"/>
+      <c r="B253" s="8"/>
+      <c r="C253" s="8"/>
       <c r="D253" s="4" t="s">
         <v>889</v>
       </c>
@@ -12409,11 +12409,11 @@
       </c>
     </row>
     <row r="254" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A254" s="9" t="s">
+      <c r="A254" s="8" t="s">
         <v>889</v>
       </c>
-      <c r="B254" s="9"/>
-      <c r="C254" s="9"/>
+      <c r="B254" s="8"/>
+      <c r="C254" s="8"/>
       <c r="D254" s="4" t="s">
         <v>892</v>
       </c>
@@ -12443,11 +12443,11 @@
       </c>
     </row>
     <row r="255" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A255" s="9" t="s">
+      <c r="A255" s="8" t="s">
         <v>895</v>
       </c>
-      <c r="B255" s="9"/>
-      <c r="C255" s="9"/>
+      <c r="B255" s="8"/>
+      <c r="C255" s="8"/>
       <c r="D255" s="4" t="s">
         <v>896</v>
       </c>
@@ -12477,11 +12477,11 @@
       </c>
     </row>
     <row r="256" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A256" s="9" t="s">
+      <c r="A256" s="8" t="s">
         <v>900</v>
       </c>
-      <c r="B256" s="9"/>
-      <c r="C256" s="9"/>
+      <c r="B256" s="8"/>
+      <c r="C256" s="8"/>
       <c r="D256" s="4" t="s">
         <v>901</v>
       </c>
@@ -12511,11 +12511,11 @@
       </c>
     </row>
     <row r="257" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A257" s="9" t="s">
+      <c r="A257" s="8" t="s">
         <v>904</v>
       </c>
-      <c r="B257" s="9"/>
-      <c r="C257" s="9"/>
+      <c r="B257" s="8"/>
+      <c r="C257" s="8"/>
       <c r="D257" s="4" t="s">
         <v>905</v>
       </c>
@@ -12545,11 +12545,11 @@
       </c>
     </row>
     <row r="258" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A258" s="9" t="s">
+      <c r="A258" s="8" t="s">
         <v>908</v>
       </c>
-      <c r="B258" s="9"/>
-      <c r="C258" s="9"/>
+      <c r="B258" s="8"/>
+      <c r="C258" s="8"/>
       <c r="D258" s="4" t="s">
         <v>909</v>
       </c>
@@ -12579,11 +12579,11 @@
       </c>
     </row>
     <row r="259" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A259" s="9" t="s">
+      <c r="A259" s="8" t="s">
         <v>912</v>
       </c>
-      <c r="B259" s="9"/>
-      <c r="C259" s="9"/>
+      <c r="B259" s="8"/>
+      <c r="C259" s="8"/>
       <c r="D259" s="4" t="s">
         <v>912</v>
       </c>
@@ -12613,11 +12613,11 @@
       </c>
     </row>
     <row r="260" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A260" s="9" t="s">
+      <c r="A260" s="8" t="s">
         <v>915</v>
       </c>
-      <c r="B260" s="9"/>
-      <c r="C260" s="9"/>
+      <c r="B260" s="8"/>
+      <c r="C260" s="8"/>
       <c r="D260" s="4" t="s">
         <v>916</v>
       </c>
@@ -12647,11 +12647,11 @@
       </c>
     </row>
     <row r="261" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A261" s="9" t="s">
+      <c r="A261" s="8" t="s">
         <v>919</v>
       </c>
-      <c r="B261" s="9"/>
-      <c r="C261" s="9"/>
+      <c r="B261" s="8"/>
+      <c r="C261" s="8"/>
       <c r="D261" s="4" t="s">
         <v>919</v>
       </c>
@@ -12681,11 +12681,11 @@
       </c>
     </row>
     <row r="262" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A262" s="9" t="s">
+      <c r="A262" s="8" t="s">
         <v>922</v>
       </c>
-      <c r="B262" s="9"/>
-      <c r="C262" s="9"/>
+      <c r="B262" s="8"/>
+      <c r="C262" s="8"/>
       <c r="D262" s="4" t="s">
         <v>923</v>
       </c>
@@ -12715,11 +12715,11 @@
       </c>
     </row>
     <row r="263" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A263" s="9" t="s">
+      <c r="A263" s="8" t="s">
         <v>925</v>
       </c>
-      <c r="B263" s="9"/>
-      <c r="C263" s="9"/>
+      <c r="B263" s="8"/>
+      <c r="C263" s="8"/>
       <c r="D263" s="4" t="s">
         <v>926</v>
       </c>
@@ -12749,11 +12749,11 @@
       </c>
     </row>
     <row r="264" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A264" s="9" t="s">
+      <c r="A264" s="8" t="s">
         <v>925</v>
       </c>
-      <c r="B264" s="9"/>
-      <c r="C264" s="9"/>
+      <c r="B264" s="8"/>
+      <c r="C264" s="8"/>
       <c r="D264" s="4" t="s">
         <v>929</v>
       </c>
@@ -12783,11 +12783,11 @@
       </c>
     </row>
     <row r="265" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A265" s="9" t="s">
+      <c r="A265" s="8" t="s">
         <v>925</v>
       </c>
-      <c r="B265" s="9"/>
-      <c r="C265" s="9"/>
+      <c r="B265" s="8"/>
+      <c r="C265" s="8"/>
       <c r="D265" s="4" t="s">
         <v>932</v>
       </c>
@@ -12817,11 +12817,11 @@
       </c>
     </row>
     <row r="266" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A266" s="9" t="s">
+      <c r="A266" s="8" t="s">
         <v>935</v>
       </c>
-      <c r="B266" s="9"/>
-      <c r="C266" s="9"/>
+      <c r="B266" s="8"/>
+      <c r="C266" s="8"/>
       <c r="D266" s="4" t="s">
         <v>935</v>
       </c>
@@ -12851,11 +12851,11 @@
       </c>
     </row>
     <row r="267" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A267" s="9" t="s">
+      <c r="A267" s="8" t="s">
         <v>938</v>
       </c>
-      <c r="B267" s="9"/>
-      <c r="C267" s="9"/>
+      <c r="B267" s="8"/>
+      <c r="C267" s="8"/>
       <c r="D267" s="4" t="s">
         <v>938</v>
       </c>
@@ -12885,11 +12885,11 @@
       </c>
     </row>
     <row r="268" spans="1:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A268" s="9" t="s">
+      <c r="A268" s="8" t="s">
         <v>941</v>
       </c>
-      <c r="B268" s="9"/>
-      <c r="C268" s="9"/>
+      <c r="B268" s="8"/>
+      <c r="C268" s="8"/>
       <c r="D268" s="4" t="s">
         <v>942</v>
       </c>
@@ -12919,11 +12919,11 @@
       </c>
     </row>
     <row r="269" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A269" s="9" t="s">
+      <c r="A269" s="8" t="s">
         <v>945</v>
       </c>
-      <c r="B269" s="9"/>
-      <c r="C269" s="9"/>
+      <c r="B269" s="8"/>
+      <c r="C269" s="8"/>
       <c r="D269" s="4" t="s">
         <v>945</v>
       </c>
@@ -12953,11 +12953,11 @@
       </c>
     </row>
     <row r="270" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A270" s="9" t="s">
+      <c r="A270" s="8" t="s">
         <v>948</v>
       </c>
-      <c r="B270" s="9"/>
-      <c r="C270" s="9"/>
+      <c r="B270" s="8"/>
+      <c r="C270" s="8"/>
       <c r="D270" s="4" t="s">
         <v>949</v>
       </c>
@@ -12987,11 +12987,11 @@
       </c>
     </row>
     <row r="271" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A271" s="9" t="s">
+      <c r="A271" s="8" t="s">
         <v>952</v>
       </c>
-      <c r="B271" s="9"/>
-      <c r="C271" s="9"/>
+      <c r="B271" s="8"/>
+      <c r="C271" s="8"/>
       <c r="D271" s="4" t="s">
         <v>953</v>
       </c>
@@ -13021,11 +13021,11 @@
       </c>
     </row>
     <row r="272" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A272" s="9" t="s">
+      <c r="A272" s="8" t="s">
         <v>956</v>
       </c>
-      <c r="B272" s="9"/>
-      <c r="C272" s="9"/>
+      <c r="B272" s="8"/>
+      <c r="C272" s="8"/>
       <c r="D272" s="4" t="s">
         <v>957</v>
       </c>
@@ -13055,11 +13055,11 @@
       </c>
     </row>
     <row r="273" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A273" s="9" t="s">
+      <c r="A273" s="8" t="s">
         <v>960</v>
       </c>
-      <c r="B273" s="9"/>
-      <c r="C273" s="9"/>
+      <c r="B273" s="8"/>
+      <c r="C273" s="8"/>
       <c r="D273" s="4" t="s">
         <v>961</v>
       </c>
@@ -13089,11 +13089,11 @@
       </c>
     </row>
     <row r="274" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A274" s="9" t="s">
+      <c r="A274" s="8" t="s">
         <v>964</v>
       </c>
-      <c r="B274" s="9"/>
-      <c r="C274" s="9"/>
+      <c r="B274" s="8"/>
+      <c r="C274" s="8"/>
       <c r="D274" s="4" t="s">
         <v>965</v>
       </c>
@@ -13123,11 +13123,11 @@
       </c>
     </row>
     <row r="275" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A275" s="9" t="s">
+      <c r="A275" s="8" t="s">
         <v>968</v>
       </c>
-      <c r="B275" s="9"/>
-      <c r="C275" s="9"/>
+      <c r="B275" s="8"/>
+      <c r="C275" s="8"/>
       <c r="D275" s="4" t="s">
         <v>969</v>
       </c>
@@ -13157,11 +13157,11 @@
       </c>
     </row>
     <row r="276" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A276" s="9" t="s">
+      <c r="A276" s="8" t="s">
         <v>972</v>
       </c>
-      <c r="B276" s="9"/>
-      <c r="C276" s="9"/>
+      <c r="B276" s="8"/>
+      <c r="C276" s="8"/>
       <c r="D276" s="4" t="s">
         <v>973</v>
       </c>
@@ -13191,11 +13191,11 @@
       </c>
     </row>
     <row r="277" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A277" s="9" t="s">
+      <c r="A277" s="8" t="s">
         <v>976</v>
       </c>
-      <c r="B277" s="9"/>
-      <c r="C277" s="9"/>
+      <c r="B277" s="8"/>
+      <c r="C277" s="8"/>
       <c r="D277" s="4" t="s">
         <v>977</v>
       </c>
@@ -13225,11 +13225,11 @@
       </c>
     </row>
     <row r="278" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A278" s="9" t="s">
+      <c r="A278" s="8" t="s">
         <v>980</v>
       </c>
-      <c r="B278" s="9"/>
-      <c r="C278" s="9"/>
+      <c r="B278" s="8"/>
+      <c r="C278" s="8"/>
       <c r="D278" s="4" t="s">
         <v>980</v>
       </c>
@@ -13259,11 +13259,11 @@
       </c>
     </row>
     <row r="279" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A279" s="9" t="s">
+      <c r="A279" s="8" t="s">
         <v>983</v>
       </c>
-      <c r="B279" s="9"/>
-      <c r="C279" s="9"/>
+      <c r="B279" s="8"/>
+      <c r="C279" s="8"/>
       <c r="D279" s="4" t="s">
         <v>983</v>
       </c>
@@ -13293,11 +13293,11 @@
       </c>
     </row>
     <row r="280" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A280" s="9" t="s">
+      <c r="A280" s="8" t="s">
         <v>986</v>
       </c>
-      <c r="B280" s="9"/>
-      <c r="C280" s="9"/>
+      <c r="B280" s="8"/>
+      <c r="C280" s="8"/>
       <c r="D280" s="4" t="s">
         <v>986</v>
       </c>
@@ -13327,11 +13327,11 @@
       </c>
     </row>
     <row r="281" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A281" s="9" t="s">
+      <c r="A281" s="8" t="s">
         <v>989</v>
       </c>
-      <c r="B281" s="9"/>
-      <c r="C281" s="9"/>
+      <c r="B281" s="8"/>
+      <c r="C281" s="8"/>
       <c r="D281" s="4" t="s">
         <v>989</v>
       </c>
@@ -13361,11 +13361,11 @@
       </c>
     </row>
     <row r="282" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A282" s="9" t="s">
+      <c r="A282" s="8" t="s">
         <v>992</v>
       </c>
-      <c r="B282" s="9"/>
-      <c r="C282" s="9"/>
+      <c r="B282" s="8"/>
+      <c r="C282" s="8"/>
       <c r="D282" s="4" t="s">
         <v>992</v>
       </c>
@@ -13395,11 +13395,11 @@
       </c>
     </row>
     <row r="283" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A283" s="9" t="s">
+      <c r="A283" s="8" t="s">
         <v>995</v>
       </c>
-      <c r="B283" s="9"/>
-      <c r="C283" s="9"/>
+      <c r="B283" s="8"/>
+      <c r="C283" s="8"/>
       <c r="D283" s="4" t="s">
         <v>996</v>
       </c>
@@ -13429,11 +13429,11 @@
       </c>
     </row>
     <row r="284" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A284" s="9" t="s">
+      <c r="A284" s="8" t="s">
         <v>999</v>
       </c>
-      <c r="B284" s="9"/>
-      <c r="C284" s="9"/>
+      <c r="B284" s="8"/>
+      <c r="C284" s="8"/>
       <c r="D284" s="4" t="s">
         <v>999</v>
       </c>
@@ -13463,11 +13463,11 @@
       </c>
     </row>
     <row r="285" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A285" s="9" t="s">
+      <c r="A285" s="8" t="s">
         <v>1002</v>
       </c>
-      <c r="B285" s="9"/>
-      <c r="C285" s="9"/>
+      <c r="B285" s="8"/>
+      <c r="C285" s="8"/>
       <c r="D285" s="4" t="s">
         <v>1002</v>
       </c>
@@ -13497,11 +13497,11 @@
       </c>
     </row>
     <row r="286" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A286" s="9" t="s">
+      <c r="A286" s="8" t="s">
         <v>1005</v>
       </c>
-      <c r="B286" s="9"/>
-      <c r="C286" s="9"/>
+      <c r="B286" s="8"/>
+      <c r="C286" s="8"/>
       <c r="D286" s="4" t="s">
         <v>1006</v>
       </c>
@@ -13531,11 +13531,11 @@
       </c>
     </row>
     <row r="287" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A287" s="9" t="s">
+      <c r="A287" s="8" t="s">
         <v>1009</v>
       </c>
-      <c r="B287" s="9"/>
-      <c r="C287" s="9"/>
+      <c r="B287" s="8"/>
+      <c r="C287" s="8"/>
       <c r="D287" s="4" t="s">
         <v>1010</v>
       </c>
@@ -13565,11 +13565,11 @@
       </c>
     </row>
     <row r="288" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A288" s="9" t="s">
+      <c r="A288" s="8" t="s">
         <v>1009</v>
       </c>
-      <c r="B288" s="9"/>
-      <c r="C288" s="9"/>
+      <c r="B288" s="8"/>
+      <c r="C288" s="8"/>
       <c r="D288" s="4" t="s">
         <v>1010</v>
       </c>
@@ -13599,11 +13599,11 @@
       </c>
     </row>
     <row r="289" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A289" s="9" t="s">
+      <c r="A289" s="8" t="s">
         <v>1009</v>
       </c>
-      <c r="B289" s="9"/>
-      <c r="C289" s="9"/>
+      <c r="B289" s="8"/>
+      <c r="C289" s="8"/>
       <c r="D289" s="4" t="s">
         <v>1014</v>
       </c>
@@ -13633,11 +13633,11 @@
       </c>
     </row>
     <row r="290" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A290" s="9" t="s">
+      <c r="A290" s="8" t="s">
         <v>1017</v>
       </c>
-      <c r="B290" s="9"/>
-      <c r="C290" s="9"/>
+      <c r="B290" s="8"/>
+      <c r="C290" s="8"/>
       <c r="D290" s="4" t="s">
         <v>1018</v>
       </c>
@@ -13667,11 +13667,11 @@
       </c>
     </row>
     <row r="291" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A291" s="9" t="s">
+      <c r="A291" s="8" t="s">
         <v>1020</v>
       </c>
-      <c r="B291" s="9"/>
-      <c r="C291" s="9"/>
+      <c r="B291" s="8"/>
+      <c r="C291" s="8"/>
       <c r="D291" s="4" t="s">
         <v>1020</v>
       </c>
@@ -13701,11 +13701,11 @@
       </c>
     </row>
     <row r="292" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A292" s="9" t="s">
+      <c r="A292" s="8" t="s">
         <v>1023</v>
       </c>
-      <c r="B292" s="9"/>
-      <c r="C292" s="9"/>
+      <c r="B292" s="8"/>
+      <c r="C292" s="8"/>
       <c r="D292" s="4" t="s">
         <v>1024</v>
       </c>
@@ -13735,11 +13735,11 @@
       </c>
     </row>
     <row r="293" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A293" s="9" t="s">
+      <c r="A293" s="8" t="s">
         <v>1027</v>
       </c>
-      <c r="B293" s="9"/>
-      <c r="C293" s="9"/>
+      <c r="B293" s="8"/>
+      <c r="C293" s="8"/>
       <c r="D293" s="4" t="s">
         <v>1028</v>
       </c>
@@ -13769,11 +13769,11 @@
       </c>
     </row>
     <row r="294" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A294" s="9" t="s">
+      <c r="A294" s="8" t="s">
         <v>1031</v>
       </c>
-      <c r="B294" s="9"/>
-      <c r="C294" s="9"/>
+      <c r="B294" s="8"/>
+      <c r="C294" s="8"/>
       <c r="D294" s="4" t="s">
         <v>1032</v>
       </c>
@@ -13803,11 +13803,11 @@
       </c>
     </row>
     <row r="295" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A295" s="9" t="s">
+      <c r="A295" s="8" t="s">
         <v>1035</v>
       </c>
-      <c r="B295" s="9"/>
-      <c r="C295" s="9"/>
+      <c r="B295" s="8"/>
+      <c r="C295" s="8"/>
       <c r="D295" s="4" t="s">
         <v>1036</v>
       </c>
@@ -13837,11 +13837,11 @@
       </c>
     </row>
     <row r="296" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A296" s="9" t="s">
+      <c r="A296" s="8" t="s">
         <v>1039</v>
       </c>
-      <c r="B296" s="9"/>
-      <c r="C296" s="9"/>
+      <c r="B296" s="8"/>
+      <c r="C296" s="8"/>
       <c r="D296" s="4" t="s">
         <v>1039</v>
       </c>
@@ -13871,11 +13871,11 @@
       </c>
     </row>
     <row r="297" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A297" s="9" t="s">
+      <c r="A297" s="8" t="s">
         <v>1042</v>
       </c>
-      <c r="B297" s="9"/>
-      <c r="C297" s="9"/>
+      <c r="B297" s="8"/>
+      <c r="C297" s="8"/>
       <c r="D297" s="4" t="s">
         <v>1043</v>
       </c>
@@ -13905,11 +13905,11 @@
       </c>
     </row>
     <row r="298" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A298" s="9" t="s">
+      <c r="A298" s="8" t="s">
         <v>1046</v>
       </c>
-      <c r="B298" s="9"/>
-      <c r="C298" s="9"/>
+      <c r="B298" s="8"/>
+      <c r="C298" s="8"/>
       <c r="D298" s="4" t="s">
         <v>1047</v>
       </c>
@@ -13939,11 +13939,11 @@
       </c>
     </row>
     <row r="299" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A299" s="9" t="s">
+      <c r="A299" s="8" t="s">
         <v>1049</v>
       </c>
-      <c r="B299" s="9"/>
-      <c r="C299" s="9"/>
+      <c r="B299" s="8"/>
+      <c r="C299" s="8"/>
       <c r="D299" s="4" t="s">
         <v>1049</v>
       </c>
@@ -13973,11 +13973,11 @@
       </c>
     </row>
     <row r="300" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A300" s="9" t="s">
+      <c r="A300" s="8" t="s">
         <v>1053</v>
       </c>
-      <c r="B300" s="9"/>
-      <c r="C300" s="9"/>
+      <c r="B300" s="8"/>
+      <c r="C300" s="8"/>
       <c r="D300" s="4" t="s">
         <v>1054</v>
       </c>
@@ -14007,11 +14007,11 @@
       </c>
     </row>
     <row r="301" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A301" s="9" t="s">
+      <c r="A301" s="8" t="s">
         <v>1057</v>
       </c>
-      <c r="B301" s="9"/>
-      <c r="C301" s="9"/>
+      <c r="B301" s="8"/>
+      <c r="C301" s="8"/>
       <c r="D301" s="4" t="s">
         <v>1057</v>
       </c>
@@ -14041,11 +14041,11 @@
       </c>
     </row>
     <row r="302" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A302" s="9" t="s">
+      <c r="A302" s="8" t="s">
         <v>1060</v>
       </c>
-      <c r="B302" s="9"/>
-      <c r="C302" s="9"/>
+      <c r="B302" s="8"/>
+      <c r="C302" s="8"/>
       <c r="D302" s="4" t="s">
         <v>1061</v>
       </c>
@@ -14075,11 +14075,11 @@
       </c>
     </row>
     <row r="303" spans="1:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A303" s="9" t="s">
+      <c r="A303" s="8" t="s">
         <v>1064</v>
       </c>
-      <c r="B303" s="9"/>
-      <c r="C303" s="9"/>
+      <c r="B303" s="8"/>
+      <c r="C303" s="8"/>
       <c r="D303" s="4" t="s">
         <v>1065</v>
       </c>
@@ -14109,11 +14109,11 @@
       </c>
     </row>
     <row r="304" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A304" s="9" t="s">
+      <c r="A304" s="8" t="s">
         <v>1068</v>
       </c>
-      <c r="B304" s="9"/>
-      <c r="C304" s="9"/>
+      <c r="B304" s="8"/>
+      <c r="C304" s="8"/>
       <c r="D304" s="4" t="s">
         <v>1069</v>
       </c>
@@ -14143,11 +14143,11 @@
       </c>
     </row>
     <row r="305" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A305" s="9" t="s">
+      <c r="A305" s="8" t="s">
         <v>1068</v>
       </c>
-      <c r="B305" s="9"/>
-      <c r="C305" s="9"/>
+      <c r="B305" s="8"/>
+      <c r="C305" s="8"/>
       <c r="D305" s="4" t="s">
         <v>1072</v>
       </c>
@@ -14177,11 +14177,11 @@
       </c>
     </row>
     <row r="306" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A306" s="9" t="s">
+      <c r="A306" s="8" t="s">
         <v>1068</v>
       </c>
-      <c r="B306" s="9"/>
-      <c r="C306" s="9"/>
+      <c r="B306" s="8"/>
+      <c r="C306" s="8"/>
       <c r="D306" s="4" t="s">
         <v>1076</v>
       </c>
@@ -14211,11 +14211,11 @@
       </c>
     </row>
     <row r="307" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A307" s="9" t="s">
+      <c r="A307" s="8" t="s">
         <v>1079</v>
       </c>
-      <c r="B307" s="9"/>
-      <c r="C307" s="9"/>
+      <c r="B307" s="8"/>
+      <c r="C307" s="8"/>
       <c r="D307" s="4" t="s">
         <v>1080</v>
       </c>
@@ -14245,11 +14245,11 @@
       </c>
     </row>
     <row r="308" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A308" s="9" t="s">
+      <c r="A308" s="8" t="s">
         <v>1083</v>
       </c>
-      <c r="B308" s="9"/>
-      <c r="C308" s="9"/>
+      <c r="B308" s="8"/>
+      <c r="C308" s="8"/>
       <c r="D308" s="4" t="s">
         <v>1083</v>
       </c>
@@ -14279,11 +14279,11 @@
       </c>
     </row>
     <row r="309" spans="1:12" ht="11.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A309" s="6" t="s">
+      <c r="A309" s="9" t="s">
         <v>1086</v>
       </c>
-      <c r="B309" s="7"/>
-      <c r="C309" s="8"/>
+      <c r="B309" s="10"/>
+      <c r="C309" s="11"/>
       <c r="D309" s="4" t="s">
         <v>1087</v>
       </c>
@@ -14313,11 +14313,11 @@
       </c>
     </row>
     <row r="310" spans="1:12" ht="11.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A310" s="6" t="s">
+      <c r="A310" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="B310" s="7"/>
-      <c r="C310" s="8"/>
+      <c r="B310" s="10"/>
+      <c r="C310" s="11"/>
       <c r="D310" s="4" t="s">
         <v>1090</v>
       </c>
@@ -14347,11 +14347,11 @@
       </c>
     </row>
     <row r="311" spans="1:12" ht="11.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A311" s="6" t="s">
+      <c r="A311" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="B311" s="7"/>
-      <c r="C311" s="8"/>
+      <c r="B311" s="10"/>
+      <c r="C311" s="11"/>
       <c r="D311" s="4" t="s">
         <v>1094</v>
       </c>
@@ -14381,11 +14381,11 @@
       </c>
     </row>
     <row r="312" spans="1:12" ht="11.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A312" s="6" t="s">
+      <c r="A312" s="9" t="s">
         <v>1097</v>
       </c>
-      <c r="B312" s="7"/>
-      <c r="C312" s="8"/>
+      <c r="B312" s="10"/>
+      <c r="C312" s="11"/>
       <c r="D312" s="4" t="s">
         <v>1097</v>
       </c>
@@ -14415,11 +14415,11 @@
       </c>
     </row>
     <row r="313" spans="1:12" ht="11.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A313" s="6" t="s">
+      <c r="A313" s="9" t="s">
         <v>1100</v>
       </c>
-      <c r="B313" s="7"/>
-      <c r="C313" s="8"/>
+      <c r="B313" s="10"/>
+      <c r="C313" s="11"/>
       <c r="D313" s="4" t="s">
         <v>1101</v>
       </c>
@@ -14449,11 +14449,11 @@
       </c>
     </row>
     <row r="314" spans="1:12" ht="11.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A314" s="6" t="s">
+      <c r="A314" s="9" t="s">
         <v>464</v>
       </c>
-      <c r="B314" s="7"/>
-      <c r="C314" s="8"/>
+      <c r="B314" s="10"/>
+      <c r="C314" s="11"/>
       <c r="D314" s="4" t="s">
         <v>1104</v>
       </c>
@@ -14483,11 +14483,11 @@
       </c>
     </row>
     <row r="315" spans="1:12" ht="11.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A315" s="6" t="s">
+      <c r="A315" s="9" t="s">
         <v>1107</v>
       </c>
-      <c r="B315" s="7"/>
-      <c r="C315" s="8"/>
+      <c r="B315" s="10"/>
+      <c r="C315" s="11"/>
       <c r="D315" s="4" t="s">
         <v>1108</v>
       </c>
@@ -14517,11 +14517,11 @@
       </c>
     </row>
     <row r="316" spans="1:12" ht="11.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A316" s="6" t="s">
+      <c r="A316" s="9" t="s">
         <v>522</v>
       </c>
-      <c r="B316" s="7"/>
-      <c r="C316" s="8"/>
+      <c r="B316" s="10"/>
+      <c r="C316" s="11"/>
       <c r="D316" s="4" t="s">
         <v>1110</v>
       </c>
@@ -14551,11 +14551,11 @@
       </c>
     </row>
     <row r="317" spans="1:12" ht="11.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A317" s="6" t="s">
+      <c r="A317" s="9" t="s">
         <v>522</v>
       </c>
-      <c r="B317" s="7"/>
-      <c r="C317" s="8"/>
+      <c r="B317" s="10"/>
+      <c r="C317" s="11"/>
       <c r="D317" s="4" t="s">
         <v>1113</v>
       </c>
@@ -14585,11 +14585,11 @@
       </c>
     </row>
     <row r="318" spans="1:12" ht="11.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A318" s="6" t="s">
+      <c r="A318" s="9" t="s">
         <v>1116</v>
       </c>
-      <c r="B318" s="7"/>
-      <c r="C318" s="8"/>
+      <c r="B318" s="10"/>
+      <c r="C318" s="11"/>
       <c r="D318" s="4" t="s">
         <v>1117</v>
       </c>
@@ -14619,11 +14619,11 @@
       </c>
     </row>
     <row r="319" spans="1:12" ht="11.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A319" s="6" t="s">
+      <c r="A319" s="9" t="s">
         <v>1119</v>
       </c>
-      <c r="B319" s="7"/>
-      <c r="C319" s="8"/>
+      <c r="B319" s="10"/>
+      <c r="C319" s="11"/>
       <c r="D319" s="4" t="s">
         <v>1120</v>
       </c>
@@ -14653,11 +14653,11 @@
       </c>
     </row>
     <row r="320" spans="1:12" ht="11.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A320" s="6" t="s">
+      <c r="A320" s="9" t="s">
         <v>1123</v>
       </c>
-      <c r="B320" s="7"/>
-      <c r="C320" s="8"/>
+      <c r="B320" s="10"/>
+      <c r="C320" s="11"/>
       <c r="D320" s="4" t="s">
         <v>1124</v>
       </c>
@@ -14687,11 +14687,11 @@
       </c>
     </row>
     <row r="321" spans="1:12" ht="11.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A321" s="6" t="s">
+      <c r="A321" s="9" t="s">
         <v>1127</v>
       </c>
-      <c r="B321" s="7"/>
-      <c r="C321" s="8"/>
+      <c r="B321" s="10"/>
+      <c r="C321" s="11"/>
       <c r="D321" s="4" t="s">
         <v>1127</v>
       </c>
@@ -14722,303 +14722,6 @@
     </row>
   </sheetData>
   <mergeCells count="318">
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A51:C51"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A55:C55"/>
-    <mergeCell ref="A56:C56"/>
-    <mergeCell ref="A57:C57"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="A59:C59"/>
-    <mergeCell ref="A60:C60"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A62:C62"/>
-    <mergeCell ref="A63:C63"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A65:C65"/>
-    <mergeCell ref="A66:C66"/>
-    <mergeCell ref="A67:C67"/>
-    <mergeCell ref="A68:C68"/>
-    <mergeCell ref="A69:C69"/>
-    <mergeCell ref="A70:C70"/>
-    <mergeCell ref="A71:C71"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A73:C73"/>
-    <mergeCell ref="A74:C74"/>
-    <mergeCell ref="A75:C75"/>
-    <mergeCell ref="A76:C76"/>
-    <mergeCell ref="A77:C77"/>
-    <mergeCell ref="A78:C78"/>
-    <mergeCell ref="A79:C79"/>
-    <mergeCell ref="A80:C80"/>
-    <mergeCell ref="A81:C81"/>
-    <mergeCell ref="A82:C82"/>
-    <mergeCell ref="A83:C83"/>
-    <mergeCell ref="A84:C84"/>
-    <mergeCell ref="A85:C85"/>
-    <mergeCell ref="A86:C86"/>
-    <mergeCell ref="A87:C87"/>
-    <mergeCell ref="A88:C88"/>
-    <mergeCell ref="A89:C89"/>
-    <mergeCell ref="A90:C90"/>
-    <mergeCell ref="A91:C91"/>
-    <mergeCell ref="A92:C92"/>
-    <mergeCell ref="A93:C93"/>
-    <mergeCell ref="A94:C94"/>
-    <mergeCell ref="A95:C95"/>
-    <mergeCell ref="A96:C96"/>
-    <mergeCell ref="A97:C97"/>
-    <mergeCell ref="A98:C98"/>
-    <mergeCell ref="A99:C99"/>
-    <mergeCell ref="A100:C100"/>
-    <mergeCell ref="A101:C101"/>
-    <mergeCell ref="A102:C102"/>
-    <mergeCell ref="A103:C103"/>
-    <mergeCell ref="A104:C104"/>
-    <mergeCell ref="A105:C105"/>
-    <mergeCell ref="A106:C106"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A108:C108"/>
-    <mergeCell ref="A109:C109"/>
-    <mergeCell ref="A110:C110"/>
-    <mergeCell ref="A111:C111"/>
-    <mergeCell ref="A112:C112"/>
-    <mergeCell ref="A113:C113"/>
-    <mergeCell ref="A114:C114"/>
-    <mergeCell ref="A115:C115"/>
-    <mergeCell ref="A116:C116"/>
-    <mergeCell ref="A117:C117"/>
-    <mergeCell ref="A118:C118"/>
-    <mergeCell ref="A119:C119"/>
-    <mergeCell ref="A120:C120"/>
-    <mergeCell ref="A121:C121"/>
-    <mergeCell ref="A122:C122"/>
-    <mergeCell ref="A123:C123"/>
-    <mergeCell ref="A124:C124"/>
-    <mergeCell ref="A125:C125"/>
-    <mergeCell ref="A126:C126"/>
-    <mergeCell ref="A127:C127"/>
-    <mergeCell ref="A128:C128"/>
-    <mergeCell ref="A129:C129"/>
-    <mergeCell ref="A130:C130"/>
-    <mergeCell ref="A131:C131"/>
-    <mergeCell ref="A132:C132"/>
-    <mergeCell ref="A133:C133"/>
-    <mergeCell ref="A134:C134"/>
-    <mergeCell ref="A135:C135"/>
-    <mergeCell ref="A136:C136"/>
-    <mergeCell ref="A137:C137"/>
-    <mergeCell ref="A138:C138"/>
-    <mergeCell ref="A139:C139"/>
-    <mergeCell ref="A140:C140"/>
-    <mergeCell ref="A141:C141"/>
-    <mergeCell ref="A142:C142"/>
-    <mergeCell ref="A143:C143"/>
-    <mergeCell ref="A144:C144"/>
-    <mergeCell ref="A145:C145"/>
-    <mergeCell ref="A146:C146"/>
-    <mergeCell ref="A147:C147"/>
-    <mergeCell ref="A148:C148"/>
-    <mergeCell ref="A149:C149"/>
-    <mergeCell ref="A150:C150"/>
-    <mergeCell ref="A151:C151"/>
-    <mergeCell ref="A152:C152"/>
-    <mergeCell ref="A153:C153"/>
-    <mergeCell ref="A154:C154"/>
-    <mergeCell ref="A155:C155"/>
-    <mergeCell ref="A156:C156"/>
-    <mergeCell ref="A157:C157"/>
-    <mergeCell ref="A158:C158"/>
-    <mergeCell ref="A159:C159"/>
-    <mergeCell ref="A160:C160"/>
-    <mergeCell ref="A161:C161"/>
-    <mergeCell ref="A162:C162"/>
-    <mergeCell ref="A163:C163"/>
-    <mergeCell ref="A164:C164"/>
-    <mergeCell ref="A165:C165"/>
-    <mergeCell ref="A166:C166"/>
-    <mergeCell ref="A167:C167"/>
-    <mergeCell ref="A168:C168"/>
-    <mergeCell ref="A169:C169"/>
-    <mergeCell ref="A170:C170"/>
-    <mergeCell ref="A171:C171"/>
-    <mergeCell ref="A172:C172"/>
-    <mergeCell ref="A173:C173"/>
-    <mergeCell ref="A174:C174"/>
-    <mergeCell ref="A175:C175"/>
-    <mergeCell ref="A176:C176"/>
-    <mergeCell ref="A177:C177"/>
-    <mergeCell ref="A178:C178"/>
-    <mergeCell ref="A179:C179"/>
-    <mergeCell ref="A180:C180"/>
-    <mergeCell ref="A181:C181"/>
-    <mergeCell ref="A182:C182"/>
-    <mergeCell ref="A183:C183"/>
-    <mergeCell ref="A184:C184"/>
-    <mergeCell ref="A185:C185"/>
-    <mergeCell ref="A186:C186"/>
-    <mergeCell ref="A187:C187"/>
-    <mergeCell ref="A188:C188"/>
-    <mergeCell ref="A189:C189"/>
-    <mergeCell ref="A190:C190"/>
-    <mergeCell ref="A191:C191"/>
-    <mergeCell ref="A192:C192"/>
-    <mergeCell ref="A193:C193"/>
-    <mergeCell ref="A194:C194"/>
-    <mergeCell ref="A195:C195"/>
-    <mergeCell ref="A196:C196"/>
-    <mergeCell ref="A197:C197"/>
-    <mergeCell ref="A198:C198"/>
-    <mergeCell ref="A199:C199"/>
-    <mergeCell ref="A200:C200"/>
-    <mergeCell ref="A201:C201"/>
-    <mergeCell ref="A202:C202"/>
-    <mergeCell ref="A203:C203"/>
-    <mergeCell ref="A204:C204"/>
-    <mergeCell ref="A205:C205"/>
-    <mergeCell ref="A206:C206"/>
-    <mergeCell ref="A207:C207"/>
-    <mergeCell ref="A208:C208"/>
-    <mergeCell ref="A209:C209"/>
-    <mergeCell ref="A210:C210"/>
-    <mergeCell ref="A211:C211"/>
-    <mergeCell ref="A212:C212"/>
-    <mergeCell ref="A213:C213"/>
-    <mergeCell ref="A214:C214"/>
-    <mergeCell ref="A215:C215"/>
-    <mergeCell ref="A216:C216"/>
-    <mergeCell ref="A217:C217"/>
-    <mergeCell ref="A218:C218"/>
-    <mergeCell ref="A219:C219"/>
-    <mergeCell ref="A220:C220"/>
-    <mergeCell ref="A221:C221"/>
-    <mergeCell ref="A222:C222"/>
-    <mergeCell ref="A223:C223"/>
-    <mergeCell ref="A224:C224"/>
-    <mergeCell ref="A225:C225"/>
-    <mergeCell ref="A226:C226"/>
-    <mergeCell ref="A227:C227"/>
-    <mergeCell ref="A228:C228"/>
-    <mergeCell ref="A229:C229"/>
-    <mergeCell ref="A230:C230"/>
-    <mergeCell ref="A231:C231"/>
-    <mergeCell ref="A232:C232"/>
-    <mergeCell ref="A233:C233"/>
-    <mergeCell ref="A234:C234"/>
-    <mergeCell ref="A235:C235"/>
-    <mergeCell ref="A236:C236"/>
-    <mergeCell ref="A237:C237"/>
-    <mergeCell ref="A238:C238"/>
-    <mergeCell ref="A239:C239"/>
-    <mergeCell ref="A240:C240"/>
-    <mergeCell ref="A241:C241"/>
-    <mergeCell ref="A242:C242"/>
-    <mergeCell ref="A243:C243"/>
-    <mergeCell ref="A244:C244"/>
-    <mergeCell ref="A245:C245"/>
-    <mergeCell ref="A246:C246"/>
-    <mergeCell ref="A247:C247"/>
-    <mergeCell ref="A248:C248"/>
-    <mergeCell ref="A249:C249"/>
-    <mergeCell ref="A250:C250"/>
-    <mergeCell ref="A251:C251"/>
-    <mergeCell ref="A252:C252"/>
-    <mergeCell ref="A253:C253"/>
-    <mergeCell ref="A254:C254"/>
-    <mergeCell ref="A255:C255"/>
-    <mergeCell ref="A256:C256"/>
-    <mergeCell ref="A257:C257"/>
-    <mergeCell ref="A258:C258"/>
-    <mergeCell ref="A259:C259"/>
-    <mergeCell ref="A260:C260"/>
-    <mergeCell ref="A261:C261"/>
-    <mergeCell ref="A262:C262"/>
-    <mergeCell ref="A263:C263"/>
-    <mergeCell ref="A264:C264"/>
-    <mergeCell ref="A265:C265"/>
-    <mergeCell ref="A266:C266"/>
-    <mergeCell ref="A267:C267"/>
-    <mergeCell ref="A268:C268"/>
-    <mergeCell ref="A269:C269"/>
-    <mergeCell ref="A270:C270"/>
-    <mergeCell ref="A271:C271"/>
-    <mergeCell ref="A272:C272"/>
-    <mergeCell ref="A273:C273"/>
-    <mergeCell ref="A274:C274"/>
-    <mergeCell ref="A275:C275"/>
-    <mergeCell ref="A276:C276"/>
-    <mergeCell ref="A277:C277"/>
-    <mergeCell ref="A278:C278"/>
-    <mergeCell ref="A279:C279"/>
-    <mergeCell ref="A280:C280"/>
-    <mergeCell ref="A281:C281"/>
-    <mergeCell ref="A282:C282"/>
-    <mergeCell ref="A283:C283"/>
-    <mergeCell ref="A284:C284"/>
-    <mergeCell ref="A285:C285"/>
-    <mergeCell ref="A286:C286"/>
-    <mergeCell ref="A287:C287"/>
-    <mergeCell ref="A288:C288"/>
-    <mergeCell ref="A289:C289"/>
-    <mergeCell ref="A290:C290"/>
-    <mergeCell ref="A291:C291"/>
-    <mergeCell ref="A292:C292"/>
-    <mergeCell ref="A293:C293"/>
-    <mergeCell ref="A294:C294"/>
-    <mergeCell ref="A295:C295"/>
-    <mergeCell ref="A296:C296"/>
-    <mergeCell ref="A297:C297"/>
-    <mergeCell ref="A298:C298"/>
-    <mergeCell ref="A299:C299"/>
-    <mergeCell ref="A300:C300"/>
     <mergeCell ref="A318:C318"/>
     <mergeCell ref="A319:C319"/>
     <mergeCell ref="A320:C320"/>
@@ -15040,6 +14743,303 @@
     <mergeCell ref="A315:C315"/>
     <mergeCell ref="A316:C316"/>
     <mergeCell ref="A317:C317"/>
+    <mergeCell ref="A292:C292"/>
+    <mergeCell ref="A293:C293"/>
+    <mergeCell ref="A294:C294"/>
+    <mergeCell ref="A295:C295"/>
+    <mergeCell ref="A296:C296"/>
+    <mergeCell ref="A297:C297"/>
+    <mergeCell ref="A298:C298"/>
+    <mergeCell ref="A299:C299"/>
+    <mergeCell ref="A300:C300"/>
+    <mergeCell ref="A283:C283"/>
+    <mergeCell ref="A284:C284"/>
+    <mergeCell ref="A285:C285"/>
+    <mergeCell ref="A286:C286"/>
+    <mergeCell ref="A287:C287"/>
+    <mergeCell ref="A288:C288"/>
+    <mergeCell ref="A289:C289"/>
+    <mergeCell ref="A290:C290"/>
+    <mergeCell ref="A291:C291"/>
+    <mergeCell ref="A274:C274"/>
+    <mergeCell ref="A275:C275"/>
+    <mergeCell ref="A276:C276"/>
+    <mergeCell ref="A277:C277"/>
+    <mergeCell ref="A278:C278"/>
+    <mergeCell ref="A279:C279"/>
+    <mergeCell ref="A280:C280"/>
+    <mergeCell ref="A281:C281"/>
+    <mergeCell ref="A282:C282"/>
+    <mergeCell ref="A265:C265"/>
+    <mergeCell ref="A266:C266"/>
+    <mergeCell ref="A267:C267"/>
+    <mergeCell ref="A268:C268"/>
+    <mergeCell ref="A269:C269"/>
+    <mergeCell ref="A270:C270"/>
+    <mergeCell ref="A271:C271"/>
+    <mergeCell ref="A272:C272"/>
+    <mergeCell ref="A273:C273"/>
+    <mergeCell ref="A256:C256"/>
+    <mergeCell ref="A257:C257"/>
+    <mergeCell ref="A258:C258"/>
+    <mergeCell ref="A259:C259"/>
+    <mergeCell ref="A260:C260"/>
+    <mergeCell ref="A261:C261"/>
+    <mergeCell ref="A262:C262"/>
+    <mergeCell ref="A263:C263"/>
+    <mergeCell ref="A264:C264"/>
+    <mergeCell ref="A247:C247"/>
+    <mergeCell ref="A248:C248"/>
+    <mergeCell ref="A249:C249"/>
+    <mergeCell ref="A250:C250"/>
+    <mergeCell ref="A251:C251"/>
+    <mergeCell ref="A252:C252"/>
+    <mergeCell ref="A253:C253"/>
+    <mergeCell ref="A254:C254"/>
+    <mergeCell ref="A255:C255"/>
+    <mergeCell ref="A238:C238"/>
+    <mergeCell ref="A239:C239"/>
+    <mergeCell ref="A240:C240"/>
+    <mergeCell ref="A241:C241"/>
+    <mergeCell ref="A242:C242"/>
+    <mergeCell ref="A243:C243"/>
+    <mergeCell ref="A244:C244"/>
+    <mergeCell ref="A245:C245"/>
+    <mergeCell ref="A246:C246"/>
+    <mergeCell ref="A229:C229"/>
+    <mergeCell ref="A230:C230"/>
+    <mergeCell ref="A231:C231"/>
+    <mergeCell ref="A232:C232"/>
+    <mergeCell ref="A233:C233"/>
+    <mergeCell ref="A234:C234"/>
+    <mergeCell ref="A235:C235"/>
+    <mergeCell ref="A236:C236"/>
+    <mergeCell ref="A237:C237"/>
+    <mergeCell ref="A220:C220"/>
+    <mergeCell ref="A221:C221"/>
+    <mergeCell ref="A222:C222"/>
+    <mergeCell ref="A223:C223"/>
+    <mergeCell ref="A224:C224"/>
+    <mergeCell ref="A225:C225"/>
+    <mergeCell ref="A226:C226"/>
+    <mergeCell ref="A227:C227"/>
+    <mergeCell ref="A228:C228"/>
+    <mergeCell ref="A211:C211"/>
+    <mergeCell ref="A212:C212"/>
+    <mergeCell ref="A213:C213"/>
+    <mergeCell ref="A214:C214"/>
+    <mergeCell ref="A215:C215"/>
+    <mergeCell ref="A216:C216"/>
+    <mergeCell ref="A217:C217"/>
+    <mergeCell ref="A218:C218"/>
+    <mergeCell ref="A219:C219"/>
+    <mergeCell ref="A202:C202"/>
+    <mergeCell ref="A203:C203"/>
+    <mergeCell ref="A204:C204"/>
+    <mergeCell ref="A205:C205"/>
+    <mergeCell ref="A206:C206"/>
+    <mergeCell ref="A207:C207"/>
+    <mergeCell ref="A208:C208"/>
+    <mergeCell ref="A209:C209"/>
+    <mergeCell ref="A210:C210"/>
+    <mergeCell ref="A193:C193"/>
+    <mergeCell ref="A194:C194"/>
+    <mergeCell ref="A195:C195"/>
+    <mergeCell ref="A196:C196"/>
+    <mergeCell ref="A197:C197"/>
+    <mergeCell ref="A198:C198"/>
+    <mergeCell ref="A199:C199"/>
+    <mergeCell ref="A200:C200"/>
+    <mergeCell ref="A201:C201"/>
+    <mergeCell ref="A184:C184"/>
+    <mergeCell ref="A185:C185"/>
+    <mergeCell ref="A186:C186"/>
+    <mergeCell ref="A187:C187"/>
+    <mergeCell ref="A188:C188"/>
+    <mergeCell ref="A189:C189"/>
+    <mergeCell ref="A190:C190"/>
+    <mergeCell ref="A191:C191"/>
+    <mergeCell ref="A192:C192"/>
+    <mergeCell ref="A175:C175"/>
+    <mergeCell ref="A176:C176"/>
+    <mergeCell ref="A177:C177"/>
+    <mergeCell ref="A178:C178"/>
+    <mergeCell ref="A179:C179"/>
+    <mergeCell ref="A180:C180"/>
+    <mergeCell ref="A181:C181"/>
+    <mergeCell ref="A182:C182"/>
+    <mergeCell ref="A183:C183"/>
+    <mergeCell ref="A166:C166"/>
+    <mergeCell ref="A167:C167"/>
+    <mergeCell ref="A168:C168"/>
+    <mergeCell ref="A169:C169"/>
+    <mergeCell ref="A170:C170"/>
+    <mergeCell ref="A171:C171"/>
+    <mergeCell ref="A172:C172"/>
+    <mergeCell ref="A173:C173"/>
+    <mergeCell ref="A174:C174"/>
+    <mergeCell ref="A157:C157"/>
+    <mergeCell ref="A158:C158"/>
+    <mergeCell ref="A159:C159"/>
+    <mergeCell ref="A160:C160"/>
+    <mergeCell ref="A161:C161"/>
+    <mergeCell ref="A162:C162"/>
+    <mergeCell ref="A163:C163"/>
+    <mergeCell ref="A164:C164"/>
+    <mergeCell ref="A165:C165"/>
+    <mergeCell ref="A148:C148"/>
+    <mergeCell ref="A149:C149"/>
+    <mergeCell ref="A150:C150"/>
+    <mergeCell ref="A151:C151"/>
+    <mergeCell ref="A152:C152"/>
+    <mergeCell ref="A153:C153"/>
+    <mergeCell ref="A154:C154"/>
+    <mergeCell ref="A155:C155"/>
+    <mergeCell ref="A156:C156"/>
+    <mergeCell ref="A139:C139"/>
+    <mergeCell ref="A140:C140"/>
+    <mergeCell ref="A141:C141"/>
+    <mergeCell ref="A142:C142"/>
+    <mergeCell ref="A143:C143"/>
+    <mergeCell ref="A144:C144"/>
+    <mergeCell ref="A145:C145"/>
+    <mergeCell ref="A146:C146"/>
+    <mergeCell ref="A147:C147"/>
+    <mergeCell ref="A130:C130"/>
+    <mergeCell ref="A131:C131"/>
+    <mergeCell ref="A132:C132"/>
+    <mergeCell ref="A133:C133"/>
+    <mergeCell ref="A134:C134"/>
+    <mergeCell ref="A135:C135"/>
+    <mergeCell ref="A136:C136"/>
+    <mergeCell ref="A137:C137"/>
+    <mergeCell ref="A138:C138"/>
+    <mergeCell ref="A121:C121"/>
+    <mergeCell ref="A122:C122"/>
+    <mergeCell ref="A123:C123"/>
+    <mergeCell ref="A124:C124"/>
+    <mergeCell ref="A125:C125"/>
+    <mergeCell ref="A126:C126"/>
+    <mergeCell ref="A127:C127"/>
+    <mergeCell ref="A128:C128"/>
+    <mergeCell ref="A129:C129"/>
+    <mergeCell ref="A112:C112"/>
+    <mergeCell ref="A113:C113"/>
+    <mergeCell ref="A114:C114"/>
+    <mergeCell ref="A115:C115"/>
+    <mergeCell ref="A116:C116"/>
+    <mergeCell ref="A117:C117"/>
+    <mergeCell ref="A118:C118"/>
+    <mergeCell ref="A119:C119"/>
+    <mergeCell ref="A120:C120"/>
+    <mergeCell ref="A103:C103"/>
+    <mergeCell ref="A104:C104"/>
+    <mergeCell ref="A105:C105"/>
+    <mergeCell ref="A106:C106"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A108:C108"/>
+    <mergeCell ref="A109:C109"/>
+    <mergeCell ref="A110:C110"/>
+    <mergeCell ref="A111:C111"/>
+    <mergeCell ref="A94:C94"/>
+    <mergeCell ref="A95:C95"/>
+    <mergeCell ref="A96:C96"/>
+    <mergeCell ref="A97:C97"/>
+    <mergeCell ref="A98:C98"/>
+    <mergeCell ref="A99:C99"/>
+    <mergeCell ref="A100:C100"/>
+    <mergeCell ref="A101:C101"/>
+    <mergeCell ref="A102:C102"/>
+    <mergeCell ref="A85:C85"/>
+    <mergeCell ref="A86:C86"/>
+    <mergeCell ref="A87:C87"/>
+    <mergeCell ref="A88:C88"/>
+    <mergeCell ref="A89:C89"/>
+    <mergeCell ref="A90:C90"/>
+    <mergeCell ref="A91:C91"/>
+    <mergeCell ref="A92:C92"/>
+    <mergeCell ref="A93:C93"/>
+    <mergeCell ref="A76:C76"/>
+    <mergeCell ref="A77:C77"/>
+    <mergeCell ref="A78:C78"/>
+    <mergeCell ref="A79:C79"/>
+    <mergeCell ref="A80:C80"/>
+    <mergeCell ref="A81:C81"/>
+    <mergeCell ref="A82:C82"/>
+    <mergeCell ref="A83:C83"/>
+    <mergeCell ref="A84:C84"/>
+    <mergeCell ref="A67:C67"/>
+    <mergeCell ref="A68:C68"/>
+    <mergeCell ref="A69:C69"/>
+    <mergeCell ref="A70:C70"/>
+    <mergeCell ref="A71:C71"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A73:C73"/>
+    <mergeCell ref="A74:C74"/>
+    <mergeCell ref="A75:C75"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A62:C62"/>
+    <mergeCell ref="A63:C63"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A65:C65"/>
+    <mergeCell ref="A66:C66"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A55:C55"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A12:C12"/>
   </mergeCells>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>
   <pageSetup fitToHeight="0" pageOrder="overThenDown" orientation="portrait"/>
